--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1884,602 +1884,1202 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_01_01</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_01</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>boss_01</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr"/>
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="M24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_02_01</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_02</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>boss_02</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr"/>
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="M25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
+      <c r="B26" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_03_01</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_03</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>boss_03</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="I26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr"/>
+      <c r="L26" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="M26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
+      <c r="B27" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_04_01</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_04</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>boss_04</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="G27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="I27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr"/>
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="M27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
+      <c r="B28" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_05_01</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_05</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>boss_05</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr"/>
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="M28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_06_01</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_06</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>boss_06</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="G29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr"/>
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="M29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
+      <c r="B30" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_07_01</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_07</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>boss_07</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="G30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="I30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr"/>
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="M30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
+      <c r="B31" s="0" t="n">
         <v>28</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_08_01</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_08</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
         <is>
           <t>boss_08</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="G31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="I31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr"/>
+      <c r="L31" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="M31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
+      <c r="B32" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_09_01</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_09</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
         <is>
           <t>boss_09</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="G32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="I32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr"/>
+      <c r="L32" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="M32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
+      <c r="B33" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_10_01</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_10</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>boss_10</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="G33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="I33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr"/>
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
+      <c r="M33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="0" t="n">
         <v>31</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_11_01</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_11</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
         <is>
           <t>boss_11</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="G34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr"/>
+      <c r="L34" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="M34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
+      <c r="B35" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_boss_final_12_01</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>wave_boss_final_12</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>boss_12</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="G35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr"/>
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t>BossEntry</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="M35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_01</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_02</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_04</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_05</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_06</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_07</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_08</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_09</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_10</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_11</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>11</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_orbit_12</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_orbit</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -2484,602 +2484,602 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_01</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="E36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="G36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
+      <c r="K36" s="0" t="inlineStr"/>
+      <c r="L36" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
+      <c r="B37" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_02</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="G37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
+      <c r="K37" s="0" t="inlineStr"/>
+      <c r="L37" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_03</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
+      <c r="G38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="0" t="n">
         <v>7.1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="K38" s="0" t="inlineStr"/>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_04</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="G39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="0" t="n">
         <v>7.1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="K39" s="0" t="inlineStr"/>
+      <c r="L39" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
+      <c r="B40" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_05</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="n">
+      <c r="G40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
+      <c r="K40" s="0" t="inlineStr"/>
+      <c r="L40" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_06</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="n">
+      <c r="G41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
+      <c r="K41" s="0" t="inlineStr"/>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_07</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="G42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="K42" s="0" t="inlineStr"/>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
+      <c r="B43" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_08</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="G43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
+      <c r="K43" s="0" t="inlineStr"/>
+      <c r="L43" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
+      <c r="B44" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_09</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="G44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
+      <c r="K44" s="0" t="inlineStr"/>
+      <c r="L44" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
+      <c r="B45" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_10</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="G45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="K45" s="0" t="inlineStr"/>
+      <c r="L45" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
+      <c r="B46" s="0" t="n">
         <v>43</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_11</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="G46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
+      <c r="K46" s="0" t="inlineStr"/>
+      <c r="L46" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
+      <c r="B47" s="0" t="n">
         <v>44</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_orbit_12</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_orbit</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="G47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,exitDirection=DownRight,exitSpeed=3.4</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
+      <c r="K47" s="0" t="inlineStr"/>
+      <c r="L47" s="0" t="inlineStr">
+        <is>
+          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+        </is>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -2520,7 +2520,7 @@
       <c r="K36" s="0" t="inlineStr"/>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
@@ -2570,7 +2570,7 @@
       <c r="K37" s="0" t="inlineStr"/>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
@@ -2620,7 +2620,7 @@
       <c r="K38" s="0" t="inlineStr"/>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
@@ -2670,7 +2670,7 @@
       <c r="K39" s="0" t="inlineStr"/>
       <c r="L39" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
@@ -2720,7 +2720,7 @@
       <c r="K40" s="0" t="inlineStr"/>
       <c r="L40" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
@@ -2770,7 +2770,7 @@
       <c r="K41" s="0" t="inlineStr"/>
       <c r="L41" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
@@ -2820,7 +2820,7 @@
       <c r="K42" s="0" t="inlineStr"/>
       <c r="L42" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
@@ -2870,7 +2870,7 @@
       <c r="K43" s="0" t="inlineStr"/>
       <c r="L43" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
@@ -2920,7 +2920,7 @@
       <c r="K44" s="0" t="inlineStr"/>
       <c r="L44" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
@@ -2970,7 +2970,7 @@
       <c r="K45" s="0" t="inlineStr"/>
       <c r="L45" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
@@ -3020,7 +3020,7 @@
       <c r="K46" s="0" t="inlineStr"/>
       <c r="L46" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M46" s="0" t="n">
@@ -3070,7 +3070,7 @@
       <c r="K47" s="0" t="inlineStr"/>
       <c r="L47" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M47" s="0" t="n">

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -2520,7 +2520,7 @@
       <c r="K36" s="0" t="inlineStr"/>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=2.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
@@ -2570,7 +2570,7 @@
       <c r="K37" s="0" t="inlineStr"/>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=2.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
@@ -2620,7 +2620,7 @@
       <c r="K38" s="0" t="inlineStr"/>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=1.75,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
@@ -2670,7 +2670,7 @@
       <c r="K39" s="0" t="inlineStr"/>
       <c r="L39" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=1.75,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
@@ -2720,7 +2720,7 @@
       <c r="K40" s="0" t="inlineStr"/>
       <c r="L40" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=1.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
@@ -2770,7 +2770,7 @@
       <c r="K41" s="0" t="inlineStr"/>
       <c r="L41" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=1.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
@@ -2820,7 +2820,7 @@
       <c r="K42" s="0" t="inlineStr"/>
       <c r="L42" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=0.75,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
@@ -2870,7 +2870,7 @@
       <c r="K43" s="0" t="inlineStr"/>
       <c r="L43" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=0.75,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
@@ -2920,7 +2920,7 @@
       <c r="K44" s="0" t="inlineStr"/>
       <c r="L44" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=0.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
@@ -2970,7 +2970,7 @@
       <c r="K45" s="0" t="inlineStr"/>
       <c r="L45" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=0.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
@@ -3020,7 +3020,7 @@
       <c r="K46" s="0" t="inlineStr"/>
       <c r="L46" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=-0.45,centerY=-0.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M46" s="0" t="n">
@@ -3070,7 +3070,7 @@
       <c r="K47" s="0" t="inlineStr"/>
       <c r="L47" s="0" t="inlineStr">
         <is>
-          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=0.22,radiusY=0.16,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
+          <t>Orbit:centerX=0.45,centerY=-0.25,radiusX=3.6,radiusY=3.6,angularSpeed=120,clockwise=false,startAngle=180,duration=0,loopCount=1,enterDuration=2.7,rotateToPath=true,rotationOffset=90,exitDirection=DownRight,exitSpeed=3.4</t>
         </is>
       </c>
       <c r="M47" s="0" t="n">

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -3083,6 +3083,1806 @@
         <v>0</v>
       </c>
     </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_01</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_02</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_03</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_04</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_05</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_06</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_07</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>7</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_08</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_09</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>9</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>55</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_11</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>11</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_left_downright_12</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_left_downright</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>12</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DriftRight</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_01</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J60" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_02</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_03</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_04</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>62</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_06</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>63</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_07</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_08</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_09</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>9</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_10</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>11</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_right_downleft_12</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_right_downleft</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>12</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>4</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>DriftLeft</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_01</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J72" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_02</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J73" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_03</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_04</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_05</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J76" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_06</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_07</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_08</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_09</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>9</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J80" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_10</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>10</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J81" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_11</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>11</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_resource_top_down_12</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>wave_level_01_resource_top_down</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>12</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>enemy_resource</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -3084,1802 +3084,1802 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
+      <c r="B48" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_01</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="E48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="G48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I48" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
+      <c r="K48" s="0" t="inlineStr"/>
+      <c r="L48" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
+      <c r="B49" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_02</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I49" t="n">
+      <c r="G49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I49" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
+      <c r="K49" s="0" t="inlineStr"/>
+      <c r="L49" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
+      <c r="B50" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_03</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="G50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I50" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
+      <c r="K50" s="0" t="inlineStr"/>
+      <c r="L50" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O50" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
+      <c r="B51" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_04</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I51" t="n">
+      <c r="G51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I51" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
+      <c r="K51" s="0" t="inlineStr"/>
+      <c r="L51" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
+      <c r="B52" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_05</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I52" t="n">
+      <c r="G52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I52" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
+      <c r="K52" s="0" t="inlineStr"/>
+      <c r="L52" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
+      <c r="B53" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_06</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="G53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I53" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
+      <c r="K53" s="0" t="inlineStr"/>
+      <c r="L53" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
+      <c r="B54" s="0" t="n">
         <v>51</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_07</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I54" t="n">
+      <c r="G54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I54" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
+      <c r="K54" s="0" t="inlineStr"/>
+      <c r="L54" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>52</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_08</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I55" t="n">
+      <c r="G55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I55" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
+      <c r="K55" s="0" t="inlineStr"/>
+      <c r="L55" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
+      <c r="B56" s="0" t="n">
         <v>53</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_09</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="G56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I56" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
+      <c r="K56" s="0" t="inlineStr"/>
+      <c r="L56" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
+      <c r="B57" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_10</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I57" t="n">
+      <c r="G57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I57" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
+      <c r="K57" s="0" t="inlineStr"/>
+      <c r="L57" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="n">
+      <c r="B58" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_11</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="G58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I58" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
+      <c r="K58" s="0" t="inlineStr"/>
+      <c r="L58" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O58" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="n">
+      <c r="B59" s="0" t="n">
         <v>56</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_left_downright_12</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_left_downright</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I59" t="n">
+      <c r="G59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I59" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>DriftRight</t>
-        </is>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
+      <c r="K59" s="0" t="inlineStr"/>
+      <c r="L59" s="0" t="inlineStr">
+        <is>
+          <t>DriftRight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
+      <c r="B60" s="0" t="n">
         <v>57</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_01</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="E60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I60" t="n">
+      <c r="G60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I60" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
+      <c r="K60" s="0" t="inlineStr"/>
+      <c r="L60" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O60" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="n">
+      <c r="B61" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_02</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I61" t="n">
+      <c r="G61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I61" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
+      <c r="K61" s="0" t="inlineStr"/>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O61" t="n">
+      <c r="O61" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="n">
+      <c r="B62" s="0" t="n">
         <v>59</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_03</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="G62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I62" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
+      <c r="K62" s="0" t="inlineStr"/>
+      <c r="L62" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="n">
+      <c r="B63" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_04</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="G63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I63" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
+      <c r="K63" s="0" t="inlineStr"/>
+      <c r="L63" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="n">
+      <c r="B64" s="0" t="n">
         <v>61</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_05</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I64" t="n">
+      <c r="G64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I64" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
+      <c r="K64" s="0" t="inlineStr"/>
+      <c r="L64" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="n">
+      <c r="B65" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_06</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="G65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I65" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
+      <c r="K65" s="0" t="inlineStr"/>
+      <c r="L65" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O65" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="n">
+      <c r="B66" s="0" t="n">
         <v>63</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_07</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="G66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I66" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
+      <c r="K66" s="0" t="inlineStr"/>
+      <c r="L66" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="n">
+      <c r="B67" s="0" t="n">
         <v>64</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_08</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I67" t="n">
+      <c r="G67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I67" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
+      <c r="K67" s="0" t="inlineStr"/>
+      <c r="L67" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M67" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="n">
+      <c r="B68" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_09</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="G68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I68" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
+      <c r="K68" s="0" t="inlineStr"/>
+      <c r="L68" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="n">
+      <c r="B69" s="0" t="n">
         <v>66</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_10</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I69" t="n">
+      <c r="G69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I69" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
+      <c r="K69" s="0" t="inlineStr"/>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>67</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_11</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I70" t="n">
+      <c r="G70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I70" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
+      <c r="K70" s="0" t="inlineStr"/>
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="n">
+      <c r="B71" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_right_downleft_12</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_right_downleft</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I71" t="n">
+      <c r="G71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I71" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>DriftLeft</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
+      <c r="K71" s="0" t="inlineStr"/>
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>DriftLeft:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="n">
+      <c r="B72" s="0" t="n">
         <v>69</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_01</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="E72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="G72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I72" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
+      <c r="K72" s="0" t="inlineStr"/>
+      <c r="L72" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="M72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="n">
+      <c r="B73" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_02</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I73" t="n">
+      <c r="G73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I73" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr"/>
+      <c r="L73" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
+      <c r="M73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="n">
+      <c r="B74" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_03</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I74" t="n">
+      <c r="G74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I74" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr"/>
+      <c r="L74" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
+      <c r="M74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="n">
+      <c r="B75" s="0" t="n">
         <v>72</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_04</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I75" t="n">
+      <c r="G75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I75" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
+      <c r="K75" s="0" t="inlineStr"/>
+      <c r="L75" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
+      <c r="M75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="n">
+      <c r="B76" s="0" t="n">
         <v>73</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_05</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I76" t="n">
+      <c r="G76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I76" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J76" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
+      <c r="K76" s="0" t="inlineStr"/>
+      <c r="L76" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
+      <c r="M76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="n">
+      <c r="B77" s="0" t="n">
         <v>74</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_06</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="G77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I77" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
+      <c r="K77" s="0" t="inlineStr"/>
+      <c r="L77" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
+      <c r="M77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="n">
+      <c r="B78" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_07</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I78" t="n">
+      <c r="G78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I78" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J78" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
+      <c r="K78" s="0" t="inlineStr"/>
+      <c r="L78" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="M78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="n">
+      <c r="B79" s="0" t="n">
         <v>76</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_08</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I79" t="n">
+      <c r="G79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I79" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="K79" s="0" t="inlineStr"/>
+      <c r="L79" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
+      <c r="M79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="n">
+      <c r="B80" s="0" t="n">
         <v>77</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_09</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I80" t="n">
+      <c r="G80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I80" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
+      <c r="K80" s="0" t="inlineStr"/>
+      <c r="L80" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
+      <c r="M80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="n">
+      <c r="B81" s="0" t="n">
         <v>78</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_10</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I81" t="n">
+      <c r="G81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I81" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J81" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
+      <c r="K81" s="0" t="inlineStr"/>
+      <c r="L81" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
+      <c r="M81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="n">
+      <c r="B82" s="0" t="n">
         <v>79</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_11</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I82" t="n">
+      <c r="G82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I82" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
+      <c r="K82" s="0" t="inlineStr"/>
+      <c r="L82" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
+      <c r="M82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="n">
+      <c r="B83" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="0" t="inlineStr">
         <is>
           <t>wave_spawn_wave_level_01_resource_top_down_12</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="0" t="inlineStr">
         <is>
           <t>wave_level_01_resource_top_down</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="0" t="inlineStr">
         <is>
           <t>enemy_resource</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I83" t="n">
+      <c r="G83" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I83" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J83" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
+      <c r="K83" s="0" t="inlineStr"/>
+      <c r="L83" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
       </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
+      <c r="M83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lipenghui/LeanProject/LeiTing/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D6131-CD0A-DE49-8B0C-BB40117C1940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5786D3E-A57D-3247-BCA3-46F740EE8653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="4080" windowWidth="33300" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="33300" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WaveSpawn" sheetId="1" r:id="rId1"/>
@@ -274,9 +274,6 @@
     <t>wave_transition_002</t>
   </si>
   <si>
-    <t>wave_spawn_wave_boss_final_01_01</t>
-  </si>
-  <si>
     <t>wave_boss_final_01</t>
   </si>
   <si>
@@ -528,6 +525,10 @@
   </si>
   <si>
     <t>enemy_ucav</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>wave_spawn_wave_boss_final_01_01</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -832,7 +833,7 @@
   <cols>
     <col min="1" max="2" width="12.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5" style="1" customWidth="1"/>
@@ -1891,17 +1892,17 @@
       <c r="B24">
         <v>21</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" t="s">
         <v>84</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
         <v>85</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>86</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1916,10 +1917,10 @@
         <v>6.2</v>
       </c>
       <c r="K24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L24" t="s">
         <v>87</v>
-      </c>
-      <c r="L24" t="s">
-        <v>88</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1936,16 +1937,16 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
         <v>89</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
         <v>90</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>91</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1960,10 +1961,10 @@
         <v>6.2</v>
       </c>
       <c r="K25" t="s">
+        <v>86</v>
+      </c>
+      <c r="L25" t="s">
         <v>87</v>
-      </c>
-      <c r="L25" t="s">
-        <v>88</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1980,16 +1981,16 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" t="s">
         <v>92</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
         <v>93</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" t="s">
-        <v>94</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2004,10 +2005,10 @@
         <v>6.2</v>
       </c>
       <c r="K26" t="s">
+        <v>86</v>
+      </c>
+      <c r="L26" t="s">
         <v>87</v>
-      </c>
-      <c r="L26" t="s">
-        <v>88</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2024,16 +2025,16 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
         <v>95</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
         <v>96</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s">
-        <v>97</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2048,10 +2049,10 @@
         <v>6.2</v>
       </c>
       <c r="K27" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27" t="s">
         <v>87</v>
-      </c>
-      <c r="L27" t="s">
-        <v>88</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2068,16 +2069,16 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
         <v>98</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
         <v>99</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" t="s">
-        <v>100</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2092,10 +2093,10 @@
         <v>6.2</v>
       </c>
       <c r="K28" t="s">
+        <v>86</v>
+      </c>
+      <c r="L28" t="s">
         <v>87</v>
-      </c>
-      <c r="L28" t="s">
-        <v>88</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -2112,16 +2113,16 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
         <v>101</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
         <v>102</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>103</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2136,10 +2137,10 @@
         <v>6.2</v>
       </c>
       <c r="K29" t="s">
+        <v>86</v>
+      </c>
+      <c r="L29" t="s">
         <v>87</v>
-      </c>
-      <c r="L29" t="s">
-        <v>88</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -2156,16 +2157,16 @@
         <v>27</v>
       </c>
       <c r="C30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" t="s">
         <v>104</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
         <v>105</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>106</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2180,10 +2181,10 @@
         <v>6.2</v>
       </c>
       <c r="K30" t="s">
+        <v>86</v>
+      </c>
+      <c r="L30" t="s">
         <v>87</v>
-      </c>
-      <c r="L30" t="s">
-        <v>88</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2200,16 +2201,16 @@
         <v>28</v>
       </c>
       <c r="C31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" t="s">
         <v>107</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
         <v>108</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" t="s">
-        <v>109</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2224,10 +2225,10 @@
         <v>6.2</v>
       </c>
       <c r="K31" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31" t="s">
         <v>87</v>
-      </c>
-      <c r="L31" t="s">
-        <v>88</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2244,16 +2245,16 @@
         <v>29</v>
       </c>
       <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
         <v>111</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" t="s">
-        <v>112</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2268,10 +2269,10 @@
         <v>6.2</v>
       </c>
       <c r="K32" t="s">
+        <v>86</v>
+      </c>
+      <c r="L32" t="s">
         <v>87</v>
-      </c>
-      <c r="L32" t="s">
-        <v>88</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2288,16 +2289,16 @@
         <v>30</v>
       </c>
       <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
         <v>113</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
         <v>114</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" t="s">
-        <v>115</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2312,10 +2313,10 @@
         <v>6.2</v>
       </c>
       <c r="K33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L33" t="s">
         <v>87</v>
-      </c>
-      <c r="L33" t="s">
-        <v>88</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2332,16 +2333,16 @@
         <v>31</v>
       </c>
       <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s">
         <v>116</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
         <v>117</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>118</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2356,10 +2357,10 @@
         <v>6.2</v>
       </c>
       <c r="K34" t="s">
+        <v>86</v>
+      </c>
+      <c r="L34" t="s">
         <v>87</v>
-      </c>
-      <c r="L34" t="s">
-        <v>88</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2376,16 +2377,16 @@
         <v>32</v>
       </c>
       <c r="C35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" t="s">
         <v>119</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
         <v>120</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" t="s">
-        <v>121</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2400,10 +2401,10 @@
         <v>6.2</v>
       </c>
       <c r="K35" t="s">
+        <v>86</v>
+      </c>
+      <c r="L35" t="s">
         <v>87</v>
-      </c>
-      <c r="L35" t="s">
-        <v>88</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2420,16 +2421,16 @@
         <v>33</v>
       </c>
       <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
         <v>122</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
         <v>123</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>124</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2444,10 +2445,10 @@
         <v>7.6</v>
       </c>
       <c r="K36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2464,16 +2465,16 @@
         <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2488,10 +2489,10 @@
         <v>7.6</v>
       </c>
       <c r="K37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2508,16 +2509,16 @@
         <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2532,10 +2533,10 @@
         <v>7.1</v>
       </c>
       <c r="K38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -2552,16 +2553,16 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E39">
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2576,10 +2577,10 @@
         <v>7.1</v>
       </c>
       <c r="K39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -2596,16 +2597,16 @@
         <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40">
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2620,10 +2621,10 @@
         <v>6.6</v>
       </c>
       <c r="K40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2640,16 +2641,16 @@
         <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2664,10 +2665,10 @@
         <v>6.6</v>
       </c>
       <c r="K41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2684,16 +2685,16 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E42">
         <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2708,10 +2709,10 @@
         <v>7.6</v>
       </c>
       <c r="K42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2728,16 +2729,16 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E43">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2752,10 +2753,10 @@
         <v>7.6</v>
       </c>
       <c r="K43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2772,16 +2773,16 @@
         <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E44">
         <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2796,10 +2797,10 @@
         <v>6.6</v>
       </c>
       <c r="K44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2816,16 +2817,16 @@
         <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2840,10 +2841,10 @@
         <v>6.6</v>
       </c>
       <c r="K45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -2860,16 +2861,16 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E46">
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2884,10 +2885,10 @@
         <v>5.6</v>
       </c>
       <c r="K46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -2904,16 +2905,16 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E47">
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2928,10 +2929,10 @@
         <v>5.6</v>
       </c>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -2948,16 +2949,16 @@
         <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2972,10 +2973,10 @@
         <v>7.6</v>
       </c>
       <c r="K48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -2992,16 +2993,16 @@
         <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E49">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3016,10 +3017,10 @@
         <v>7.6</v>
       </c>
       <c r="K49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3036,16 +3037,16 @@
         <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E50">
         <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -3060,10 +3061,10 @@
         <v>6.6</v>
       </c>
       <c r="K50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -3080,16 +3081,16 @@
         <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -3104,10 +3105,10 @@
         <v>6.6</v>
       </c>
       <c r="K51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3124,16 +3125,16 @@
         <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E52">
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -3148,10 +3149,10 @@
         <v>5.6</v>
       </c>
       <c r="K52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3168,16 +3169,16 @@
         <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E53">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3192,10 +3193,10 @@
         <v>5.6</v>
       </c>
       <c r="K53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -3212,16 +3213,16 @@
         <v>69</v>
       </c>
       <c r="C54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" t="s">
         <v>152</v>
       </c>
-      <c r="D54" t="s">
-        <v>153</v>
-      </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -3236,7 +3237,7 @@
         <v>10.6</v>
       </c>
       <c r="K54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L54" t="s">
         <v>37</v>
@@ -3256,16 +3257,16 @@
         <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E55">
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3280,7 +3281,7 @@
         <v>10.6</v>
       </c>
       <c r="K55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L55" t="s">
         <v>37</v>
@@ -3300,16 +3301,16 @@
         <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E56">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3324,7 +3325,7 @@
         <v>9.6</v>
       </c>
       <c r="K56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L56" t="s">
         <v>37</v>
@@ -3344,16 +3345,16 @@
         <v>72</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E57">
         <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -3368,7 +3369,7 @@
         <v>9.6</v>
       </c>
       <c r="K57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L57" t="s">
         <v>37</v>
@@ -3388,16 +3389,16 @@
         <v>73</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E58">
         <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3412,7 +3413,7 @@
         <v>8.6</v>
       </c>
       <c r="K58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L58" t="s">
         <v>37</v>
@@ -3432,16 +3433,16 @@
         <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D59" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E59">
         <v>6</v>
       </c>
       <c r="F59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -3456,7 +3457,7 @@
         <v>8.6</v>
       </c>
       <c r="K59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L59" t="s">
         <v>37</v>
@@ -3476,16 +3477,16 @@
         <v>75</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E60">
         <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3500,7 +3501,7 @@
         <v>7.6</v>
       </c>
       <c r="K60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L60" t="s">
         <v>37</v>
@@ -3520,16 +3521,16 @@
         <v>76</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E61">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -3544,7 +3545,7 @@
         <v>7.6</v>
       </c>
       <c r="K61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L61" t="s">
         <v>37</v>
@@ -3564,16 +3565,16 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D62" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E62">
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3588,7 +3589,7 @@
         <v>6.6</v>
       </c>
       <c r="K62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L62" t="s">
         <v>37</v>
@@ -3608,16 +3609,16 @@
         <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E63">
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -3632,7 +3633,7 @@
         <v>6.6</v>
       </c>
       <c r="K63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L63" t="s">
         <v>37</v>
@@ -3652,16 +3653,16 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D64" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E64">
         <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3676,7 +3677,7 @@
         <v>5.6</v>
       </c>
       <c r="K64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L64" t="s">
         <v>37</v>
@@ -3696,16 +3697,16 @@
         <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E65">
         <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -3720,7 +3721,7 @@
         <v>5.6</v>
       </c>
       <c r="K65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L65" t="s">
         <v>37</v>
@@ -3741,16 +3742,16 @@
         <v>81</v>
       </c>
       <c r="C66" t="s">
+        <v>164</v>
+      </c>
+      <c r="D66" t="s">
         <v>165</v>
       </c>
-      <c r="D66" t="s">
-        <v>166</v>
-      </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3765,7 +3766,7 @@
         <v>7</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L66" t="s">
         <v>44</v>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -3781,6 +3781,114 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="67" spans="1:15" ht="16">
+      <c r="B67">
+        <v>82</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wave_spawn_wave_level_01_spiral_045_left</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wave_level_01_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy_ucav</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0.1</v>
+      </c>
+      <c r="I67">
+        <v>-4</v>
+      </c>
+      <c r="J67">
+        <v>7</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy_spiral_windmill</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StopAndLeave</t>
+        </is>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="16">
+      <c r="B68">
+        <v>83</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wave_spawn_wave_level_01_spiral_045_right</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wave_level_01_spiral_045_sides</t>
+        </is>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy_ucav</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0.1</v>
+      </c>
+      <c r="I68">
+        <v>4</v>
+      </c>
+      <c r="J68">
+        <v>7</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enemy_spiral_windmill</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StopAndLeave</t>
+        </is>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>5.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -372,7 +372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_extra_planes_073_01</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_left_01</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_extra_planes_073</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E70" s="0" t="n">
@@ -4052,26 +4052,22 @@
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>enemy_a</t>
+          <t>level1_side_helicopter</t>
         </is>
       </c>
       <c r="G70" s="0" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H70" s="0" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I70" s="0" t="n">
-        <v>0</v>
+        <v>-3.25</v>
       </c>
       <c r="J70" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="K70" s="0" t="inlineStr">
-        <is>
-          <t>enemy_aim_single</t>
-        </is>
-      </c>
+      <c r="K70" s="0" t="n"/>
       <c r="L70" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
@@ -4089,46 +4085,42 @@
     </row>
     <row r="71">
       <c r="B71" s="0" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_homing_fighters_080_01</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_left_02</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_homing_fighters_080</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E71" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t>level1_homing_fighter</t>
+          <t>level1_side_helicopter</t>
         </is>
       </c>
       <c r="G71" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H71" s="0" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="I71" s="0" t="n">
-        <v>0</v>
+        <v>-3.25</v>
       </c>
       <c r="J71" s="0" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K71" s="0" t="inlineStr">
-        <is>
-          <t>level1_fighter_homing_pair</t>
-        </is>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="K71" s="0" t="n"/>
       <c r="L71" s="0" t="inlineStr">
         <is>
-          <t>StopAndLeave:fireOnce=true,fireOnceDelay=0.75,rotateToPath=true,rotationOffset=90</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="M71" s="0" t="n">
@@ -4138,29 +4130,29 @@
         <v>0</v>
       </c>
       <c r="O71" s="0" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="0" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_midboss_090_01</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_left_03</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_midboss_090</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E72" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t>boss_level1_enemy_08</t>
+          <t>level1_side_helicopter</t>
         </is>
       </c>
       <c r="G72" s="0" t="n">
@@ -4170,15 +4162,15 @@
         <v>0.1</v>
       </c>
       <c r="I72" s="0" t="n">
-        <v>0</v>
+        <v>-3.25</v>
       </c>
       <c r="J72" s="0" t="n">
-        <v>6.2</v>
+        <v>10.3</v>
       </c>
       <c r="K72" s="0" t="n"/>
       <c r="L72" s="0" t="inlineStr">
         <is>
-          <t>BossEntry</t>
+          <t>Straight</t>
         </is>
       </c>
       <c r="M72" s="0" t="n">
@@ -4193,20 +4185,20 @@
     </row>
     <row r="73">
       <c r="B73" s="0" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_left_01</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_left_04</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E73" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
@@ -4223,7 +4215,7 @@
         <v>-3.25</v>
       </c>
       <c r="J73" s="0" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="K73" s="0" t="n"/>
       <c r="L73" s="0" t="inlineStr">
@@ -4243,20 +4235,20 @@
     </row>
     <row r="74">
       <c r="B74" s="0" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_right_01</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_left_05</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E74" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
@@ -4270,10 +4262,10 @@
         <v>0.1</v>
       </c>
       <c r="I74" s="0" t="n">
-        <v>3.25</v>
+        <v>-3.25</v>
       </c>
       <c r="J74" s="0" t="n">
-        <v>5.9</v>
+        <v>14.7</v>
       </c>
       <c r="K74" s="0" t="n"/>
       <c r="L74" s="0" t="inlineStr">
@@ -4293,20 +4285,20 @@
     </row>
     <row r="75">
       <c r="B75" s="0" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_left_02</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_right_01</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E75" s="0" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
@@ -4320,10 +4312,10 @@
         <v>0.1</v>
       </c>
       <c r="I75" s="0" t="n">
-        <v>-3.25</v>
+        <v>3.25</v>
       </c>
       <c r="J75" s="0" t="n">
-        <v>6.55</v>
+        <v>5.9</v>
       </c>
       <c r="K75" s="0" t="n"/>
       <c r="L75" s="0" t="inlineStr">
@@ -4343,16 +4335,16 @@
     </row>
     <row r="76">
       <c r="B76" s="0" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_right_02</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_right_02</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E76" s="0" t="n">
@@ -4373,7 +4365,7 @@
         <v>3.25</v>
       </c>
       <c r="J76" s="0" t="n">
-        <v>6.55</v>
+        <v>8.1</v>
       </c>
       <c r="K76" s="0" t="n"/>
       <c r="L76" s="0" t="inlineStr">
@@ -4393,20 +4385,20 @@
     </row>
     <row r="77">
       <c r="B77" s="0" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_left_03</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_right_03</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E77" s="0" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
@@ -4420,10 +4412,10 @@
         <v>0.1</v>
       </c>
       <c r="I77" s="0" t="n">
-        <v>-3.25</v>
+        <v>3.25</v>
       </c>
       <c r="J77" s="0" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="K77" s="0" t="n"/>
       <c r="L77" s="0" t="inlineStr">
@@ -4443,20 +4435,20 @@
     </row>
     <row r="78">
       <c r="B78" s="0" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_right_03</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_right_04</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E78" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
@@ -4473,7 +4465,7 @@
         <v>3.25</v>
       </c>
       <c r="J78" s="0" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="K78" s="0" t="n"/>
       <c r="L78" s="0" t="inlineStr">
@@ -4493,20 +4485,20 @@
     </row>
     <row r="79">
       <c r="B79" s="0" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_left_04</t>
+          <t>wave_spawn_wave_level_01_side_helis_073_right_05</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_side_helis_073</t>
         </is>
       </c>
       <c r="E79" s="0" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
@@ -4520,10 +4512,10 @@
         <v>0.1</v>
       </c>
       <c r="I79" s="0" t="n">
-        <v>-3.25</v>
+        <v>3.25</v>
       </c>
       <c r="J79" s="0" t="n">
-        <v>7.85</v>
+        <v>14.7</v>
       </c>
       <c r="K79" s="0" t="n"/>
       <c r="L79" s="0" t="inlineStr">
@@ -4543,42 +4535,46 @@
     </row>
     <row r="80">
       <c r="B80" s="0" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_right_04</t>
+          <t>wave_spawn_wave_level_01_homing_fighters_080_01</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_homing_fighters_080</t>
         </is>
       </c>
       <c r="E80" s="0" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>level1_side_helicopter</t>
+          <t>level1_homing_fighter</t>
         </is>
       </c>
       <c r="G80" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H80" s="0" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="I80" s="0" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="J80" s="0" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="K80" s="0" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="K80" s="0" t="inlineStr">
+        <is>
+          <t>level1_fighter_homing_pair</t>
+        </is>
+      </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>StopAndLeave:fireOnce=true,fireOnceDelay=0.75,rotateToPath=true,rotationOffset=90</t>
         </is>
       </c>
       <c r="M80" s="0" t="n">
@@ -4588,29 +4584,29 @@
         <v>0</v>
       </c>
       <c r="O80" s="0" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_left_05</t>
+          <t>wave_spawn_wave_level_01_enemy_08_test_002_01</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>wave_level_01_side_helis_110</t>
+          <t>wave_level_01_enemy_08_test_002</t>
         </is>
       </c>
       <c r="E81" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>level1_side_helicopter</t>
+          <t>level1_enemy_08</t>
         </is>
       </c>
       <c r="G81" s="0" t="n">
@@ -4620,15 +4616,19 @@
         <v>0.1</v>
       </c>
       <c r="I81" s="0" t="n">
-        <v>-3.25</v>
+        <v>0</v>
       </c>
       <c r="J81" s="0" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K81" s="0" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="K81" s="0" t="inlineStr">
+        <is>
+          <t>level1_midboss_center_random_line@3+0.2|level1_midboss_windmill_cw@4+0.6|level1_midboss_windmill_ccw@4+2.6|level1_midboss_missile_pair@6+1.2</t>
+        </is>
+      </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="M81" s="0" t="n">
@@ -4643,11 +4643,11 @@
     </row>
     <row r="82">
       <c r="B82" s="0" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>wave_spawn_wave_level_01_side_helis_110_right_05</t>
+          <t>wave_spawn_wave_level_01_side_helis_110_left_01</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="E82" s="0" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
@@ -4670,10 +4670,10 @@
         <v>0.1</v>
       </c>
       <c r="I82" s="0" t="n">
-        <v>3.25</v>
+        <v>-3.25</v>
       </c>
       <c r="J82" s="0" t="n">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="K82" s="0" t="n"/>
       <c r="L82" s="0" t="inlineStr">
@@ -4688,6 +4688,456 @@
         <v>0</v>
       </c>
       <c r="O82" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_right_01</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I83" s="0" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J83" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K83" s="0" t="n"/>
+      <c r="L83" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_left_02</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I84" s="0" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="J84" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K84" s="0" t="n"/>
+      <c r="L84" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_right_02</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I85" s="0" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J85" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K85" s="0" t="n"/>
+      <c r="L85" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_left_03</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I86" s="0" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="J86" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K86" s="0" t="n"/>
+      <c r="L86" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_right_03</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I87" s="0" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J87" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K87" s="0" t="n"/>
+      <c r="L87" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_left_04</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I88" s="0" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="J88" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K88" s="0" t="n"/>
+      <c r="L88" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_right_04</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I89" s="0" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J89" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K89" s="0" t="n"/>
+      <c r="L89" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_left_05</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G90" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I90" s="0" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="J90" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K90" s="0" t="n"/>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_side_helis_110_right_05</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_side_helis_110</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>level1_side_helicopter</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I91" s="0" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J91" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K91" s="0" t="n"/>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t>Straight</t>
+        </is>
+      </c>
+      <c r="M91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -372,7 +372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -5141,6 +5141,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="92">
+      <c r="B92" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_split_fighters_130_left_pair</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>level1_split_fighter</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" s="0" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I92" s="0" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J92" s="0" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="K92" s="0" t="inlineStr">
+        <is>
+          <t>level1_split_fighter_split@3+0.65</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>Straight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>wave_spawn_wave_level_01_split_fighters_130_right_pair</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t>wave_level_01_split_fighters_130</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>level1_split_fighter</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="0" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I93" s="0" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J93" s="0" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="K93" s="0" t="inlineStr">
+        <is>
+          <t>level1_split_fighter_split@3+0.65</t>
+        </is>
+      </c>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t>Straight:rotateToPath=true,rotationOffset=90</t>
+        </is>
+      </c>
+      <c r="M93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/WaveSpawn.xlsx
+++ b/Luban/Datas/WaveSpawn.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="1" r:id="R9f0ca4c1e5d44cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawn" sheetId="1" r:id="Re1823729b0ea403f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -417,9 +417,10 @@
     <x:col min="13" max="13" width="22.3046875" style="3" customWidth="1"/>
     <x:col min="14" max="14" width="16.3046875" style="3" customWidth="1"/>
     <x:col min="15" max="15" width="12.3046875" style="3" customWidth="1"/>
-    <x:col min="16" max="16" width="15.3046875" style="3" customWidth="1"/>
+    <x:col min="16" max="16" width="20" style="3" hidden="0" customWidth="1"/>
     <x:col min="17" max="21" width="8.84375" style="3" customWidth="1"/>
     <x:col min="22" max="16384" width="8.84375" style="3" customWidth="1"/>
+    <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -498,6 +499,12 @@
           <x:t xml:space="preserve">holdDuration</x:t>
         </x:is>
       </x:c>
+      <x:c r="P1" t="str">
+        <x:v>dropItemId</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>dropIndex</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="inlineStr">
@@ -575,6 +582,12 @@
           <x:t xml:space="preserve">float</x:t>
         </x:is>
       </x:c>
+      <x:c r="P2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="inlineStr">
@@ -647,6 +660,12 @@
         <x:is>
           <x:t xml:space="preserve">停留时间</x:t>
         </x:is>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>固定掉落物ID</x:v>
+      </x:c>
+      <x:c r="Q3" t="str">
+        <x:v>组内携带者序号（从1开始，0表示无）</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -701,6 +720,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" t="str"/>
+      <x:c r="Q4" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -758,6 +781,10 @@
       <x:c r="O5" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P5" t="str"/>
+      <x:c r="Q5" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="6" t="n"/>
@@ -813,6 +840,10 @@
       <x:c r="O6" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P6" t="str"/>
+      <x:c r="Q6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="6" t="n"/>
@@ -868,6 +899,10 @@
       <x:c r="O7" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P7" t="str"/>
+      <x:c r="Q7" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="n"/>
@@ -923,6 +958,10 @@
       <x:c r="O8" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P8" t="str"/>
+      <x:c r="Q8" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6" t="n"/>
@@ -978,6 +1017,10 @@
       <x:c r="O9" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P9" t="str"/>
+      <x:c r="Q9" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6" t="n"/>
@@ -1033,6 +1076,10 @@
       <x:c r="O10" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P10" t="str"/>
+      <x:c r="Q10" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="6" t="n"/>
@@ -1088,6 +1135,10 @@
       <x:c r="O11" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P11" t="str"/>
+      <x:c r="Q11" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="n"/>
@@ -1143,6 +1194,10 @@
       <x:c r="O12" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P12" t="str"/>
+      <x:c r="Q12" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="6" t="n"/>
@@ -1198,6 +1253,10 @@
       <x:c r="O13" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P13" t="str"/>
+      <x:c r="Q13" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="6" t="n"/>
@@ -1253,6 +1312,10 @@
       <x:c r="O14" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P14" t="str"/>
+      <x:c r="Q14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="6" t="n"/>
@@ -1308,6 +1371,10 @@
       <x:c r="O15" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P15" t="str"/>
+      <x:c r="Q15" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="6" t="n"/>
@@ -1363,6 +1430,10 @@
       <x:c r="O16" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P16" t="str"/>
+      <x:c r="Q16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="6" t="n"/>
@@ -1418,6 +1489,10 @@
       <x:c r="O17" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P17" t="str"/>
+      <x:c r="Q17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="6" t="n"/>
@@ -1473,6 +1548,10 @@
       <x:c r="O18" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P18" t="str"/>
+      <x:c r="Q18" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="6" t="n"/>
@@ -1528,6 +1607,10 @@
       <x:c r="O19" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P19" t="str"/>
+      <x:c r="Q19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="6" t="n"/>
@@ -1583,6 +1666,10 @@
       <x:c r="O20" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P20" t="str"/>
+      <x:c r="Q20" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="6" t="n"/>
@@ -1638,6 +1725,10 @@
       <x:c r="O21" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P21" t="str"/>
+      <x:c r="Q21" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="6" t="n"/>
@@ -1693,6 +1784,10 @@
       <x:c r="O22" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P22" t="str"/>
+      <x:c r="Q22" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="6" t="n"/>
@@ -1748,6 +1843,10 @@
       <x:c r="O23" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P23" t="str"/>
+      <x:c r="Q23" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A24" s="6" t="n"/>
@@ -1799,6 +1898,10 @@
       <x:c r="O24" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P24" t="str"/>
+      <x:c r="Q24" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A25" s="6" t="n"/>
@@ -1850,6 +1953,10 @@
       <x:c r="O25" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P25" t="str"/>
+      <x:c r="Q25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A26" s="6" t="n"/>
@@ -1901,6 +2008,10 @@
       <x:c r="O26" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P26" t="str"/>
+      <x:c r="Q26" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A27" s="6" t="n"/>
@@ -1952,6 +2063,10 @@
       <x:c r="O27" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P27" t="str"/>
+      <x:c r="Q27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A28" s="6" t="n"/>
@@ -2003,6 +2118,10 @@
       <x:c r="O28" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P28" t="str"/>
+      <x:c r="Q28" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A29" s="6" t="n"/>
@@ -2054,6 +2173,10 @@
       <x:c r="O29" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P29" t="str"/>
+      <x:c r="Q29" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A30" s="6" t="n"/>
@@ -2105,6 +2228,10 @@
       <x:c r="O30" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P30" t="str"/>
+      <x:c r="Q30" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A31" s="6" t="n"/>
@@ -2156,6 +2283,10 @@
       <x:c r="O31" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P31" t="str"/>
+      <x:c r="Q31" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A32" s="6" t="n"/>
@@ -2207,6 +2338,10 @@
       <x:c r="O32" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P32" t="str"/>
+      <x:c r="Q32" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A33" s="6" t="n"/>
@@ -2258,6 +2393,10 @@
       <x:c r="O33" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P33" t="str"/>
+      <x:c r="Q33" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A34" s="6" t="n"/>
@@ -2309,6 +2448,10 @@
       <x:c r="O34" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P34" t="str"/>
+      <x:c r="Q34" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A35" s="6" t="n"/>
@@ -2360,6 +2503,10 @@
       <x:c r="O35" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P35" t="str"/>
+      <x:c r="Q35" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A36" s="6" t="n"/>
@@ -2411,6 +2558,10 @@
       <x:c r="O36" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P36" t="str"/>
+      <x:c r="Q36" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A37" s="6" t="n"/>
@@ -2462,6 +2613,10 @@
       <x:c r="O37" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P37" t="str"/>
+      <x:c r="Q37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A38" s="6" t="n"/>
@@ -2513,6 +2668,10 @@
       <x:c r="O38" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P38" t="str"/>
+      <x:c r="Q38" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A39" s="6" t="n"/>
@@ -2564,6 +2723,10 @@
       <x:c r="O39" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P39" t="str"/>
+      <x:c r="Q39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A40" s="6" t="n"/>
@@ -2615,6 +2778,10 @@
       <x:c r="O40" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P40" t="str"/>
+      <x:c r="Q40" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A41" s="6" t="n"/>
@@ -2666,6 +2833,10 @@
       <x:c r="O41" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P41" t="str"/>
+      <x:c r="Q41" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A42" s="6" t="n"/>
@@ -2717,6 +2888,10 @@
       <x:c r="O42" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P42" t="str"/>
+      <x:c r="Q42" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A43" s="6" t="n"/>
@@ -2768,6 +2943,10 @@
       <x:c r="O43" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P43" t="str"/>
+      <x:c r="Q43" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A44" s="6" t="n"/>
@@ -2819,6 +2998,10 @@
       <x:c r="O44" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P44" t="str"/>
+      <x:c r="Q44" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A45" s="6" t="n"/>
@@ -2870,6 +3053,10 @@
       <x:c r="O45" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P45" t="str"/>
+      <x:c r="Q45" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A46" s="6" t="n"/>
@@ -2921,6 +3108,10 @@
       <x:c r="O46" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P46" t="str"/>
+      <x:c r="Q46" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A47" s="6" t="n"/>
@@ -2972,6 +3163,10 @@
       <x:c r="O47" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P47" t="str"/>
+      <x:c r="Q47" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A48" s="6" t="n"/>
@@ -3023,6 +3218,10 @@
       <x:c r="O48" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P48" t="str"/>
+      <x:c r="Q48" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A49" s="6" t="n"/>
@@ -3074,6 +3273,10 @@
       <x:c r="O49" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P49" t="str"/>
+      <x:c r="Q49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A50" s="6" t="n"/>
@@ -3125,6 +3328,10 @@
       <x:c r="O50" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P50" t="str"/>
+      <x:c r="Q50" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A51" s="6" t="n"/>
@@ -3176,6 +3383,10 @@
       <x:c r="O51" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P51" t="str"/>
+      <x:c r="Q51" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A52" s="6" t="n"/>
@@ -3227,6 +3438,10 @@
       <x:c r="O52" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P52" t="str"/>
+      <x:c r="Q52" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A53" s="6" t="n"/>
@@ -3278,6 +3493,10 @@
       <x:c r="O53" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P53" t="str"/>
+      <x:c r="Q53" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A54" s="6" t="n"/>
@@ -3329,6 +3548,10 @@
       <x:c r="O54" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P54" t="str"/>
+      <x:c r="Q54" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A55" s="6" t="n"/>
@@ -3380,6 +3603,10 @@
       <x:c r="O55" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P55" t="str"/>
+      <x:c r="Q55" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A56" s="6" t="n"/>
@@ -3435,6 +3662,10 @@
       <x:c r="O56" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P56" t="str"/>
+      <x:c r="Q56" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A57" s="6" t="n"/>
@@ -3490,6 +3721,10 @@
       <x:c r="O57" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P57" t="str"/>
+      <x:c r="Q57" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A58" s="6" t="n"/>
@@ -3545,6 +3780,10 @@
       <x:c r="O58" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P58" t="str"/>
+      <x:c r="Q58" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A59" s="6" t="n"/>
@@ -3596,6 +3835,10 @@
       <x:c r="O59" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P59" t="str"/>
+      <x:c r="Q59" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A60" s="6" t="n"/>
@@ -3647,6 +3890,10 @@
       <x:c r="O60" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P60" t="str"/>
+      <x:c r="Q60" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A61" s="6" t="n"/>
@@ -3698,6 +3945,10 @@
       <x:c r="O61" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P61" t="str"/>
+      <x:c r="Q61" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A62" s="6" t="n"/>
@@ -3749,6 +4000,10 @@
       <x:c r="O62" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P62" t="str"/>
+      <x:c r="Q62" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A63" s="6" t="n"/>
@@ -3800,6 +4055,10 @@
       <x:c r="O63" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P63" t="str"/>
+      <x:c r="Q63" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A64" s="6" t="n"/>
@@ -3851,6 +4110,10 @@
       <x:c r="O64" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P64" t="str"/>
+      <x:c r="Q64" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A65" s="6" t="n"/>
@@ -3902,6 +4165,10 @@
       <x:c r="O65" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P65" t="str"/>
+      <x:c r="Q65" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A66" s="6" t="n"/>
@@ -3953,6 +4220,10 @@
       <x:c r="O66" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P66" t="str"/>
+      <x:c r="Q66" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A67" s="6" t="n"/>
@@ -4004,6 +4275,10 @@
       <x:c r="O67" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P67" t="str"/>
+      <x:c r="Q67" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A68" s="6" t="n"/>
@@ -4055,6 +4330,10 @@
       <x:c r="O68" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P68" t="str"/>
+      <x:c r="Q68" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A69" s="6" t="n"/>
@@ -4106,6 +4385,10 @@
       <x:c r="O69" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P69" t="str"/>
+      <x:c r="Q69" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A70" s="6" t="n"/>
@@ -4161,6 +4444,10 @@
       <x:c r="O70" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P70" t="str"/>
+      <x:c r="Q70" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A71" s="6" t="n"/>
@@ -4216,6 +4503,10 @@
       <x:c r="O71" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P71" t="str"/>
+      <x:c r="Q71" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A72" s="6" t="n"/>
@@ -4267,6 +4558,10 @@
       <x:c r="O72" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P72" t="str"/>
+      <x:c r="Q72" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A73" s="6" t="n"/>
@@ -4318,6 +4613,10 @@
       <x:c r="O73" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P73" t="str"/>
+      <x:c r="Q73" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A74" s="6" t="n"/>
@@ -4369,6 +4668,10 @@
       <x:c r="O74" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P74" t="str"/>
+      <x:c r="Q74" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A75" s="6" t="n"/>
@@ -4420,6 +4723,10 @@
       <x:c r="O75" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P75" t="str"/>
+      <x:c r="Q75" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A76" s="6" t="n"/>
@@ -4471,6 +4778,10 @@
       <x:c r="O76" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P76" t="str"/>
+      <x:c r="Q76" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A77" s="6" t="n"/>
@@ -4522,6 +4833,10 @@
       <x:c r="O77" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P77" t="str"/>
+      <x:c r="Q77" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A78" s="6" t="n"/>
@@ -4573,6 +4888,10 @@
       <x:c r="O78" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P78" t="str"/>
+      <x:c r="Q78" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A79" s="6" t="n"/>
@@ -4624,6 +4943,10 @@
       <x:c r="O79" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P79" t="str"/>
+      <x:c r="Q79" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A80" s="6" t="n"/>
@@ -4675,6 +4998,10 @@
       <x:c r="O80" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P80" t="str"/>
+      <x:c r="Q80" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A81" s="6" t="n"/>
@@ -4726,6 +5053,10 @@
       <x:c r="O81" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P81" t="str"/>
+      <x:c r="Q81" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A82" s="6" t="n"/>
@@ -4781,6 +5112,10 @@
       <x:c r="O82" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P82" t="str"/>
+      <x:c r="Q82" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A83" s="6" t="n"/>
@@ -4836,6 +5171,10 @@
       <x:c r="O83" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P83" t="str"/>
+      <x:c r="Q83" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A84" s="6" t="n"/>
@@ -4887,6 +5226,12 @@
       <x:c r="O84" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P84" t="str">
+        <x:v>weaponup</x:v>
+      </x:c>
+      <x:c r="Q84" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A85" s="6" t="n"/>
@@ -4938,6 +5283,10 @@
       <x:c r="O85" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P85" t="str"/>
+      <x:c r="Q85" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A86" s="6" t="n"/>
@@ -4989,6 +5338,10 @@
       <x:c r="O86" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P86" t="str"/>
+      <x:c r="Q86" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A87" s="6" t="n"/>
@@ -5040,6 +5393,12 @@
       <x:c r="O87" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P87" t="str">
+        <x:v>weaponup</x:v>
+      </x:c>
+      <x:c r="Q87" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A88" s="6" t="n"/>
@@ -5091,6 +5450,12 @@
       <x:c r="O88" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P88" t="str">
+        <x:v>weaponup</x:v>
+      </x:c>
+      <x:c r="Q88" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A89" s="6" t="n"/>
@@ -5142,6 +5507,10 @@
       <x:c r="O89" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P89" t="str"/>
+      <x:c r="Q89" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A90" s="6" t="n"/>
@@ -5193,6 +5562,10 @@
       <x:c r="O90" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P90" t="str"/>
+      <x:c r="Q90" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A91" s="6" t="n"/>
@@ -5248,6 +5621,10 @@
       <x:c r="O91" s="6" t="n">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="P91" t="str"/>
+      <x:c r="Q91" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A92" s="6" t="n"/>
@@ -5303,6 +5680,10 @@
       <x:c r="O92" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P92" t="str"/>
+      <x:c r="Q92" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" s="12" customFormat="1" ht="16" customHeight="1">
       <x:c r="A93" s="6" t="n"/>
@@ -5358,6 +5739,10 @@
       <x:c r="O93" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P93" t="str"/>
+      <x:c r="Q93" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="94" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A94" s="6" t="n"/>
@@ -5413,6 +5798,10 @@
       <x:c r="O94" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P94" t="str"/>
+      <x:c r="Q94" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A95" s="6" t="n"/>
@@ -5468,6 +5857,10 @@
       <x:c r="O95" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P95" t="str"/>
+      <x:c r="Q95" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A96" s="6" t="n"/>
@@ -5523,6 +5916,10 @@
       <x:c r="O96" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P96" t="str"/>
+      <x:c r="Q96" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A97" s="6" t="n"/>
@@ -5578,6 +5975,10 @@
       <x:c r="O97" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P97" t="str"/>
+      <x:c r="Q97" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A98" s="6" t="n"/>
@@ -5633,6 +6034,10 @@
       <x:c r="O98" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P98" t="str"/>
+      <x:c r="Q98" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A99" s="6" t="n"/>
@@ -5688,6 +6093,10 @@
       <x:c r="O99" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P99" t="str"/>
+      <x:c r="Q99" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A100" s="6" t="n"/>
@@ -5743,6 +6152,10 @@
       <x:c r="O100" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P100" t="str"/>
+      <x:c r="Q100" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A101" s="6" t="n"/>
@@ -5798,6 +6211,10 @@
       <x:c r="O101" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P101" t="str"/>
+      <x:c r="Q101" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" s="7" customFormat="1" ht="16" customHeight="1">
       <x:c r="A102" s="6" t="n"/>
@@ -5853,6 +6270,10 @@
       <x:c r="O102" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P102" t="str"/>
+      <x:c r="Q102" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="6" t="n"/>
@@ -5908,6 +6329,10 @@
       <x:c r="O103" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P103" t="str"/>
+      <x:c r="Q103" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="6" t="n"/>
@@ -5963,6 +6388,10 @@
       <x:c r="O104" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P104" t="str"/>
+      <x:c r="Q104" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="6" t="n"/>
@@ -6018,6 +6447,10 @@
       <x:c r="O105" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P105" t="str"/>
+      <x:c r="Q105" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="6" t="n"/>
@@ -6073,6 +6506,10 @@
       <x:c r="O106" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P106" t="str"/>
+      <x:c r="Q106" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="6" t="n"/>
@@ -6128,6 +6565,10 @@
       <x:c r="O107" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P107" t="str"/>
+      <x:c r="Q107" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="6" t="n"/>
@@ -6183,6 +6624,10 @@
       <x:c r="O108" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P108" t="str"/>
+      <x:c r="Q108" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="6" t="n"/>
@@ -6238,6 +6683,10 @@
       <x:c r="O109" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P109" t="str"/>
+      <x:c r="Q109" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="6" t="n"/>
@@ -6293,6 +6742,10 @@
       <x:c r="O110" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P110" t="str"/>
+      <x:c r="Q110" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="6" t="n"/>
@@ -6348,6 +6801,10 @@
       <x:c r="O111" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P111" t="str"/>
+      <x:c r="Q111" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="6" t="n"/>
@@ -6399,6 +6856,10 @@
       <x:c r="O112" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P112" t="str"/>
+      <x:c r="Q112" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="6" t="n"/>
@@ -6450,6 +6911,10 @@
       <x:c r="O113" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P113" t="str"/>
+      <x:c r="Q113" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="6" t="n"/>
@@ -6501,6 +6966,10 @@
       <x:c r="O114" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P114" t="str"/>
+      <x:c r="Q114" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="6" t="n"/>
@@ -6552,6 +7021,10 @@
       <x:c r="O115" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P115" t="str"/>
+      <x:c r="Q115" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="6" t="n"/>
@@ -6603,6 +7076,10 @@
       <x:c r="O116" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P116" t="str"/>
+      <x:c r="Q116" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="6" t="n"/>
@@ -6654,6 +7131,10 @@
       <x:c r="O117" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P117" t="str"/>
+      <x:c r="Q117" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="6" t="n"/>
@@ -6705,6 +7186,10 @@
       <x:c r="O118" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P118" t="str"/>
+      <x:c r="Q118" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="6" t="n"/>
@@ -6756,6 +7241,10 @@
       <x:c r="O119" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P119" t="str"/>
+      <x:c r="Q119" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="6" t="n"/>
@@ -6807,6 +7296,10 @@
       <x:c r="O120" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P120" t="str"/>
+      <x:c r="Q120" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="6" t="n"/>
@@ -6858,6 +7351,10 @@
       <x:c r="O121" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P121" t="str"/>
+      <x:c r="Q121" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="6" t="n"/>
@@ -6909,6 +7406,10 @@
       <x:c r="O122" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P122" t="str"/>
+      <x:c r="Q122" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="6" t="n"/>
@@ -6960,6 +7461,10 @@
       <x:c r="O123" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P123" t="str"/>
+      <x:c r="Q123" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="6" t="n"/>
@@ -7011,6 +7516,10 @@
       <x:c r="O124" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P124" t="str"/>
+      <x:c r="Q124" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="6" t="n"/>
@@ -7062,6 +7571,10 @@
       <x:c r="O125" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P125" t="str"/>
+      <x:c r="Q125" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="6" t="n"/>
@@ -7113,6 +7626,10 @@
       <x:c r="O126" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P126" t="str"/>
+      <x:c r="Q126" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="6" t="n"/>
@@ -7164,6 +7681,10 @@
       <x:c r="O127" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P127" t="str"/>
+      <x:c r="Q127" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="6" t="n"/>
@@ -7215,6 +7736,10 @@
       <x:c r="O128" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P128" t="str"/>
+      <x:c r="Q128" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="6" t="n"/>
@@ -7266,6 +7791,10 @@
       <x:c r="O129" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P129" t="str"/>
+      <x:c r="Q129" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="6" t="n"/>
@@ -7317,6 +7846,10 @@
       <x:c r="O130" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P130" t="str"/>
+      <x:c r="Q130" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="6" t="n"/>
@@ -7368,6 +7901,10 @@
       <x:c r="O131" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P131" t="str"/>
+      <x:c r="Q131" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="6" t="n"/>
@@ -7419,6 +7956,10 @@
       <x:c r="O132" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P132" t="str"/>
+      <x:c r="Q132" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="6" t="n"/>
@@ -7470,6 +8011,10 @@
       <x:c r="O133" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P133" t="str"/>
+      <x:c r="Q133" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="6" t="n"/>
@@ -7521,6 +8066,10 @@
       <x:c r="O134" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P134" t="str"/>
+      <x:c r="Q134" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="6" t="n"/>
@@ -7572,6 +8121,10 @@
       <x:c r="O135" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P135" t="str"/>
+      <x:c r="Q135" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="6" t="n"/>
@@ -7623,6 +8176,10 @@
       <x:c r="O136" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P136" t="str"/>
+      <x:c r="Q136" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="6" t="n"/>
@@ -7674,6 +8231,10 @@
       <x:c r="O137" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P137" t="str"/>
+      <x:c r="Q137" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="6" t="n"/>
@@ -7725,6 +8286,10 @@
       <x:c r="O138" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P138" t="str"/>
+      <x:c r="Q138" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="6" t="n"/>
@@ -7776,6 +8341,10 @@
       <x:c r="O139" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P139" t="str"/>
+      <x:c r="Q139" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="6" t="n"/>
@@ -7827,6 +8396,10 @@
       <x:c r="O140" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P140" t="str"/>
+      <x:c r="Q140" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="6" t="n"/>
@@ -7878,6 +8451,10 @@
       <x:c r="O141" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P141" t="str"/>
+      <x:c r="Q141" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="6" t="n"/>
@@ -7929,6 +8506,10 @@
       <x:c r="O142" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P142" t="str"/>
+      <x:c r="Q142" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="6" t="n"/>
@@ -7984,6 +8565,10 @@
       <x:c r="O143" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P143" t="str"/>
+      <x:c r="Q143" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="6" t="n"/>
@@ -8039,6 +8624,10 @@
       <x:c r="O144" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P144" t="str"/>
+      <x:c r="Q144" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="6" t="n"/>
@@ -8094,6 +8683,10 @@
       <x:c r="O145" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P145" t="str"/>
+      <x:c r="Q145" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="6" t="n"/>
@@ -8145,6 +8738,10 @@
       <x:c r="O146" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P146" t="str"/>
+      <x:c r="Q146" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="6" t="n"/>
@@ -8196,6 +8793,10 @@
       <x:c r="O147" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P147" t="str"/>
+      <x:c r="Q147" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="6" t="n"/>
@@ -8247,6 +8848,10 @@
       <x:c r="O148" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P148" t="str"/>
+      <x:c r="Q148" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="6" t="n"/>
@@ -8298,6 +8903,10 @@
       <x:c r="O149" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P149" t="str"/>
+      <x:c r="Q149" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="6" t="n"/>
@@ -8349,6 +8958,10 @@
       <x:c r="O150" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P150" t="str"/>
+      <x:c r="Q150" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="6" t="n"/>
@@ -8400,6 +9013,10 @@
       <x:c r="O151" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P151" t="str"/>
+      <x:c r="Q151" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="6" t="n"/>
@@ -8451,6 +9068,10 @@
       <x:c r="O152" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P152" t="str"/>
+      <x:c r="Q152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="6" t="n"/>
@@ -8502,6 +9123,10 @@
       <x:c r="O153" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P153" t="str"/>
+      <x:c r="Q153" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="6" t="n"/>
@@ -8553,6 +9178,10 @@
       <x:c r="O154" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P154" t="str"/>
+      <x:c r="Q154" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="6" t="n"/>
@@ -8604,6 +9233,10 @@
       <x:c r="O155" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P155" t="str"/>
+      <x:c r="Q155" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="6" t="n"/>
@@ -8655,6 +9288,10 @@
       <x:c r="O156" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P156" t="str"/>
+      <x:c r="Q156" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="6" t="n"/>
@@ -8710,6 +9347,10 @@
       <x:c r="O157" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P157" t="str"/>
+      <x:c r="Q157" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="6" t="n"/>
@@ -8765,6 +9406,10 @@
       <x:c r="O158" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P158" t="str"/>
+      <x:c r="Q158" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="6" t="n"/>
@@ -8816,6 +9461,10 @@
       <x:c r="O159" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P159" t="str"/>
+      <x:c r="Q159" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="6" t="n"/>
@@ -8867,6 +9516,10 @@
       <x:c r="O160" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P160" t="str"/>
+      <x:c r="Q160" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="6" t="n"/>
@@ -8918,6 +9571,10 @@
       <x:c r="O161" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P161" t="str"/>
+      <x:c r="Q161" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="6" t="n"/>
@@ -8969,6 +9626,10 @@
       <x:c r="O162" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P162" t="str"/>
+      <x:c r="Q162" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="6" t="n"/>
@@ -9020,6 +9681,10 @@
       <x:c r="O163" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P163" t="str"/>
+      <x:c r="Q163" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="6" t="n"/>
@@ -9071,6 +9736,10 @@
       <x:c r="O164" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P164" t="str"/>
+      <x:c r="Q164" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="6" t="n"/>
@@ -9122,6 +9791,10 @@
       <x:c r="O165" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P165" t="str"/>
+      <x:c r="Q165" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="6" t="n"/>
@@ -9173,6 +9846,10 @@
       <x:c r="O166" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P166" t="str"/>
+      <x:c r="Q166" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="6" t="n"/>
@@ -9224,6 +9901,10 @@
       <x:c r="O167" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P167" t="str"/>
+      <x:c r="Q167" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="6" t="n"/>
@@ -9275,6 +9956,10 @@
       <x:c r="O168" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P168" t="str"/>
+      <x:c r="Q168" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="6" t="n"/>
@@ -9330,6 +10015,10 @@
       <x:c r="O169" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P169" t="str"/>
+      <x:c r="Q169" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="6" t="n"/>
@@ -9385,6 +10074,10 @@
       <x:c r="O170" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P170" t="str"/>
+      <x:c r="Q170" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="6" t="n"/>
@@ -9440,6 +10133,10 @@
       <x:c r="O171" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P171" t="str"/>
+      <x:c r="Q171" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="6" t="n"/>
@@ -9495,6 +10192,10 @@
       <x:c r="O172" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P172" t="str"/>
+      <x:c r="Q172" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="6" t="n"/>
@@ -9550,6 +10251,10 @@
       <x:c r="O173" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P173" t="str"/>
+      <x:c r="Q173" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="6" t="n"/>
@@ -9605,6 +10310,10 @@
       <x:c r="O174" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P174" t="str"/>
+      <x:c r="Q174" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="6" t="n"/>
@@ -9660,6 +10369,10 @@
       <x:c r="O175" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P175" t="str"/>
+      <x:c r="Q175" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="6" t="n"/>
@@ -9715,6 +10428,10 @@
       <x:c r="O176" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P176" t="str"/>
+      <x:c r="Q176" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="6" t="n"/>
@@ -9770,6 +10487,10 @@
       <x:c r="O177" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P177" t="str"/>
+      <x:c r="Q177" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="6" t="n"/>
@@ -9825,6 +10546,10 @@
       <x:c r="O178" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P178" t="str"/>
+      <x:c r="Q178" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="6" t="n"/>
@@ -9880,6 +10605,10 @@
       <x:c r="O179" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P179" t="str"/>
+      <x:c r="Q179" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="6" t="n"/>
@@ -9935,6 +10664,10 @@
       <x:c r="O180" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P180" t="str"/>
+      <x:c r="Q180" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="6" t="n"/>
@@ -9990,6 +10723,10 @@
       <x:c r="O181" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P181" t="str"/>
+      <x:c r="Q181" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="6" t="n"/>
@@ -10045,6 +10782,10 @@
       <x:c r="O182" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P182" t="str"/>
+      <x:c r="Q182" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="6" t="n"/>
@@ -10100,6 +10841,10 @@
       <x:c r="O183" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P183" t="str"/>
+      <x:c r="Q183" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="6" t="n"/>
@@ -10155,6 +10900,10 @@
       <x:c r="O184" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P184" t="str"/>
+      <x:c r="Q184" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="6" t="n"/>
@@ -10210,6 +10959,10 @@
       <x:c r="O185" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P185" t="str"/>
+      <x:c r="Q185" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="6" t="n"/>
@@ -10265,6 +11018,10 @@
       <x:c r="O186" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P186" t="str"/>
+      <x:c r="Q186" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="6" t="n"/>
@@ -10320,6 +11077,10 @@
       <x:c r="O187" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P187" t="str"/>
+      <x:c r="Q187" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="6" t="n"/>
@@ -10375,6 +11136,10 @@
       <x:c r="O188" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P188" t="str"/>
+      <x:c r="Q188" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="6" t="n"/>
@@ -10430,6 +11195,10 @@
       <x:c r="O189" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P189" t="str"/>
+      <x:c r="Q189" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="6" t="n"/>
@@ -10485,6 +11254,10 @@
       <x:c r="O190" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P190" t="str"/>
+      <x:c r="Q190" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="6" t="n"/>
@@ -10536,6 +11309,10 @@
       <x:c r="O191" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P191" t="str"/>
+      <x:c r="Q191" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="6" t="n"/>
@@ -10587,6 +11364,10 @@
       <x:c r="O192" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P192" t="str"/>
+      <x:c r="Q192" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="6" t="n"/>
@@ -10638,6 +11419,10 @@
       <x:c r="O193" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P193" t="str"/>
+      <x:c r="Q193" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="6" t="n"/>
@@ -10689,6 +11474,10 @@
       <x:c r="O194" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P194" t="str"/>
+      <x:c r="Q194" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="6" t="n"/>
@@ -10740,6 +11529,10 @@
       <x:c r="O195" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P195" t="str"/>
+      <x:c r="Q195" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="6" t="n"/>
@@ -10791,6 +11584,10 @@
       <x:c r="O196" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P196" t="str"/>
+      <x:c r="Q196" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="6" t="n"/>
@@ -10842,6 +11639,10 @@
       <x:c r="O197" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P197" t="str"/>
+      <x:c r="Q197" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="6" t="n"/>
@@ -10893,6 +11694,10 @@
       <x:c r="O198" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P198" t="str"/>
+      <x:c r="Q198" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="6" t="n"/>
@@ -10944,6 +11749,10 @@
       <x:c r="O199" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P199" t="str"/>
+      <x:c r="Q199" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="6" t="n"/>
@@ -10995,6 +11804,10 @@
       <x:c r="O200" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P200" t="str"/>
+      <x:c r="Q200" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="6" t="n"/>
@@ -11046,6 +11859,10 @@
       <x:c r="O201" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P201" t="str"/>
+      <x:c r="Q201" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="6" t="n"/>
@@ -11097,6 +11914,10 @@
       <x:c r="O202" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P202" t="str"/>
+      <x:c r="Q202" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="6" t="n"/>
@@ -11148,6 +11969,10 @@
       <x:c r="O203" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P203" t="str"/>
+      <x:c r="Q203" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="6" t="n"/>
@@ -11199,6 +12024,10 @@
       <x:c r="O204" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P204" t="str"/>
+      <x:c r="Q204" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="6" t="n"/>
@@ -11250,6 +12079,10 @@
       <x:c r="O205" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P205" t="str"/>
+      <x:c r="Q205" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="6" t="n"/>
@@ -11301,6 +12134,10 @@
       <x:c r="O206" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P206" t="str"/>
+      <x:c r="Q206" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="6" t="n"/>
@@ -11352,6 +12189,10 @@
       <x:c r="O207" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P207" t="str"/>
+      <x:c r="Q207" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="6" t="n"/>
@@ -11403,6 +12244,10 @@
       <x:c r="O208" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P208" t="str"/>
+      <x:c r="Q208" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="6" t="n"/>
@@ -11454,6 +12299,10 @@
       <x:c r="O209" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P209" t="str"/>
+      <x:c r="Q209" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="6" t="n"/>
@@ -11505,6 +12354,10 @@
       <x:c r="O210" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P210" t="str"/>
+      <x:c r="Q210" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="6" t="n"/>
@@ -11556,6 +12409,10 @@
       <x:c r="O211" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P211" t="str"/>
+      <x:c r="Q211" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="6" t="n"/>
@@ -11607,6 +12464,10 @@
       <x:c r="O212" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P212" t="str"/>
+      <x:c r="Q212" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="6" t="n"/>
@@ -11658,6 +12519,10 @@
       <x:c r="O213" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P213" t="str"/>
+      <x:c r="Q213" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="6" t="n"/>
@@ -11709,6 +12574,10 @@
       <x:c r="O214" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P214" t="str"/>
+      <x:c r="Q214" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="6" t="n"/>
@@ -11760,6 +12629,10 @@
       <x:c r="O215" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P215" t="str"/>
+      <x:c r="Q215" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="6" t="n"/>
@@ -11811,6 +12684,10 @@
       <x:c r="O216" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P216" t="str"/>
+      <x:c r="Q216" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="6" t="n"/>
@@ -11862,6 +12739,10 @@
       <x:c r="O217" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P217" t="str"/>
+      <x:c r="Q217" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="6" t="n"/>
@@ -11913,6 +12794,10 @@
       <x:c r="O218" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P218" t="str"/>
+      <x:c r="Q218" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="6" t="n"/>
@@ -11964,6 +12849,10 @@
       <x:c r="O219" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P219" t="str"/>
+      <x:c r="Q219" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="6" t="n"/>
@@ -12015,6 +12904,10 @@
       <x:c r="O220" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P220" t="str"/>
+      <x:c r="Q220" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="6" t="n"/>
@@ -12066,6 +12959,10 @@
       <x:c r="O221" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P221" t="str"/>
+      <x:c r="Q221" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="6" t="n"/>
@@ -12121,6 +13018,10 @@
       <x:c r="O222" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P222" t="str"/>
+      <x:c r="Q222" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="6" t="n"/>
@@ -12176,6 +13077,10 @@
       <x:c r="O223" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P223" t="str"/>
+      <x:c r="Q223" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="6" t="n"/>
@@ -12231,6 +13136,10 @@
       <x:c r="O224" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P224" t="str"/>
+      <x:c r="Q224" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="6" t="n"/>
@@ -12282,6 +13191,10 @@
       <x:c r="O225" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P225" t="str"/>
+      <x:c r="Q225" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="6" t="n"/>
@@ -12333,6 +13246,10 @@
       <x:c r="O226" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P226" t="str"/>
+      <x:c r="Q226" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="6" t="n"/>
@@ -12384,6 +13301,10 @@
       <x:c r="O227" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P227" t="str"/>
+      <x:c r="Q227" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="6" t="n"/>
@@ -12435,6 +13356,10 @@
       <x:c r="O228" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P228" t="str"/>
+      <x:c r="Q228" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="6" t="n"/>
@@ -12486,6 +13411,10 @@
       <x:c r="O229" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P229" t="str"/>
+      <x:c r="Q229" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="6" t="n"/>
@@ -12537,6 +13466,10 @@
       <x:c r="O230" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P230" t="str"/>
+      <x:c r="Q230" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="6" t="n"/>
@@ -12588,6 +13521,10 @@
       <x:c r="O231" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P231" t="str"/>
+      <x:c r="Q231" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="6" t="n"/>
@@ -12639,6 +13576,10 @@
       <x:c r="O232" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P232" t="str"/>
+      <x:c r="Q232" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="6" t="n"/>
@@ -12690,6 +13631,10 @@
       <x:c r="O233" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P233" t="str"/>
+      <x:c r="Q233" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="6" t="n"/>
@@ -12741,6 +13686,10 @@
       <x:c r="O234" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P234" t="str"/>
+      <x:c r="Q234" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="6" t="n"/>
@@ -12792,6 +13741,10 @@
       <x:c r="O235" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P235" t="str"/>
+      <x:c r="Q235" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="6" t="n"/>
@@ -12847,6 +13800,10 @@
       <x:c r="O236" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P236" t="str"/>
+      <x:c r="Q236" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="6" t="n"/>
@@ -12902,6 +13859,10 @@
       <x:c r="O237" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P237" t="str"/>
+      <x:c r="Q237" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="6" t="n"/>
@@ -12953,6 +13914,10 @@
       <x:c r="O238" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P238" t="str"/>
+      <x:c r="Q238" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="6" t="n"/>
@@ -13004,6 +13969,10 @@
       <x:c r="O239" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P239" t="str"/>
+      <x:c r="Q239" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="6" t="n"/>
@@ -13055,6 +14024,10 @@
       <x:c r="O240" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P240" t="str"/>
+      <x:c r="Q240" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="6" t="n"/>
@@ -13106,6 +14079,10 @@
       <x:c r="O241" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P241" t="str"/>
+      <x:c r="Q241" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="6" t="n"/>
@@ -13157,6 +14134,10 @@
       <x:c r="O242" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P242" t="str"/>
+      <x:c r="Q242" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="6" t="n"/>
@@ -13208,6 +14189,10 @@
       <x:c r="O243" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P243" t="str"/>
+      <x:c r="Q243" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="6" t="n"/>
@@ -13259,6 +14244,10 @@
       <x:c r="O244" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P244" t="str"/>
+      <x:c r="Q244" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="6" t="n"/>
@@ -13310,6 +14299,10 @@
       <x:c r="O245" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P245" t="str"/>
+      <x:c r="Q245" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="6" t="n"/>
@@ -13361,6 +14354,10 @@
       <x:c r="O246" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P246" t="str"/>
+      <x:c r="Q246" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="6" t="n"/>
@@ -13412,6 +14409,10 @@
       <x:c r="O247" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P247" t="str"/>
+      <x:c r="Q247" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="6" t="n"/>
@@ -13467,6 +14468,10 @@
       <x:c r="O248" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P248" t="str"/>
+      <x:c r="Q248" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="6" t="n"/>
@@ -13522,6 +14527,10 @@
       <x:c r="O249" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P249" t="str"/>
+      <x:c r="Q249" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="6" t="n"/>
@@ -13577,6 +14586,10 @@
       <x:c r="O250" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P250" t="str"/>
+      <x:c r="Q250" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="6" t="n"/>
@@ -13632,6 +14645,10 @@
       <x:c r="O251" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P251" t="str"/>
+      <x:c r="Q251" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="6" t="n"/>
@@ -13687,6 +14704,10 @@
       <x:c r="O252" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P252" t="str"/>
+      <x:c r="Q252" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="6" t="n"/>
@@ -13742,6 +14763,10 @@
       <x:c r="O253" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P253" t="str"/>
+      <x:c r="Q253" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="6" t="n"/>
@@ -13797,6 +14822,10 @@
       <x:c r="O254" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P254" t="str"/>
+      <x:c r="Q254" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="6" t="n"/>
@@ -13852,6 +14881,10 @@
       <x:c r="O255" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P255" t="str"/>
+      <x:c r="Q255" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="6" t="n"/>
@@ -13907,6 +14940,10 @@
       <x:c r="O256" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P256" t="str"/>
+      <x:c r="Q256" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="6" t="n"/>
@@ -13962,6 +14999,10 @@
       <x:c r="O257" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P257" t="str"/>
+      <x:c r="Q257" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="6" t="n"/>
@@ -14017,6 +15058,10 @@
       <x:c r="O258" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P258" t="str"/>
+      <x:c r="Q258" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="6" t="n"/>
@@ -14072,6 +15117,10 @@
       <x:c r="O259" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P259" t="str"/>
+      <x:c r="Q259" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="6" t="n"/>
@@ -14127,6 +15176,10 @@
       <x:c r="O260" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P260" t="str"/>
+      <x:c r="Q260" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="6" t="n"/>
@@ -14182,6 +15235,10 @@
       <x:c r="O261" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P261" t="str"/>
+      <x:c r="Q261" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="6" t="n"/>
@@ -14237,6 +15294,10 @@
       <x:c r="O262" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P262" t="str"/>
+      <x:c r="Q262" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="6" t="n"/>
@@ -14292,6 +15353,10 @@
       <x:c r="O263" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P263" t="str"/>
+      <x:c r="Q263" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="6" t="n"/>
@@ -14347,6 +15412,10 @@
       <x:c r="O264" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P264" t="str"/>
+      <x:c r="Q264" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="6" t="n"/>
@@ -14402,6 +15471,10 @@
       <x:c r="O265" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P265" t="str"/>
+      <x:c r="Q265" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="6" t="n"/>
@@ -14457,6 +15530,10 @@
       <x:c r="O266" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P266" t="str"/>
+      <x:c r="Q266" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="6" t="n"/>
@@ -14512,6 +15589,10 @@
       <x:c r="O267" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P267" t="str"/>
+      <x:c r="Q267" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="6" t="n"/>
@@ -14567,6 +15648,10 @@
       <x:c r="O268" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P268" t="str"/>
+      <x:c r="Q268" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="6" t="n"/>
@@ -14622,6 +15707,10 @@
       <x:c r="O269" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P269" t="str"/>
+      <x:c r="Q269" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="6" t="n"/>
@@ -14673,6 +15762,10 @@
       <x:c r="O270" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P270" t="str"/>
+      <x:c r="Q270" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="6" t="n"/>
@@ -14724,6 +15817,10 @@
       <x:c r="O271" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P271" t="str"/>
+      <x:c r="Q271" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="6" t="n"/>
@@ -14775,6 +15872,10 @@
       <x:c r="O272" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P272" t="str"/>
+      <x:c r="Q272" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="6" t="n"/>
@@ -14826,6 +15927,10 @@
       <x:c r="O273" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P273" t="str"/>
+      <x:c r="Q273" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="6" t="n"/>
@@ -14877,6 +15982,10 @@
       <x:c r="O274" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P274" t="str"/>
+      <x:c r="Q274" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="6" t="n"/>
@@ -14928,6 +16037,10 @@
       <x:c r="O275" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P275" t="str"/>
+      <x:c r="Q275" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="6" t="n"/>
@@ -14979,6 +16092,10 @@
       <x:c r="O276" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P276" t="str"/>
+      <x:c r="Q276" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="6" t="n"/>
@@ -15030,6 +16147,10 @@
       <x:c r="O277" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P277" t="str"/>
+      <x:c r="Q277" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="6" t="n"/>
@@ -15081,6 +16202,10 @@
       <x:c r="O278" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P278" t="str"/>
+      <x:c r="Q278" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="6" t="n"/>
@@ -15132,6 +16257,10 @@
       <x:c r="O279" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P279" t="str"/>
+      <x:c r="Q279" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="6" t="n"/>
@@ -15183,6 +16312,10 @@
       <x:c r="O280" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P280" t="str"/>
+      <x:c r="Q280" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="6" t="n"/>
@@ -15234,6 +16367,10 @@
       <x:c r="O281" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P281" t="str"/>
+      <x:c r="Q281" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="6" t="n"/>
@@ -15285,6 +16422,10 @@
       <x:c r="O282" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P282" t="str"/>
+      <x:c r="Q282" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="6" t="n"/>
@@ -15336,6 +16477,10 @@
       <x:c r="O283" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P283" t="str"/>
+      <x:c r="Q283" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="6" t="n"/>
@@ -15387,6 +16532,10 @@
       <x:c r="O284" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P284" t="str"/>
+      <x:c r="Q284" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="6" t="n"/>
@@ -15438,6 +16587,10 @@
       <x:c r="O285" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P285" t="str"/>
+      <x:c r="Q285" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="6" t="n"/>
@@ -15489,6 +16642,10 @@
       <x:c r="O286" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P286" t="str"/>
+      <x:c r="Q286" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="6" t="n"/>
@@ -15540,6 +16697,10 @@
       <x:c r="O287" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P287" t="str"/>
+      <x:c r="Q287" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="6" t="n"/>
@@ -15591,6 +16752,10 @@
       <x:c r="O288" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P288" t="str"/>
+      <x:c r="Q288" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="6" t="n"/>
@@ -15642,6 +16807,10 @@
       <x:c r="O289" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P289" t="str"/>
+      <x:c r="Q289" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="6" t="n"/>
@@ -15693,6 +16862,10 @@
       <x:c r="O290" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P290" t="str"/>
+      <x:c r="Q290" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="6" t="n"/>
@@ -15744,6 +16917,10 @@
       <x:c r="O291" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P291" t="str"/>
+      <x:c r="Q291" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="6" t="n"/>
@@ -15795,6 +16972,10 @@
       <x:c r="O292" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P292" t="str"/>
+      <x:c r="Q292" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="6" t="n"/>
@@ -15846,6 +17027,10 @@
       <x:c r="O293" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P293" t="str"/>
+      <x:c r="Q293" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="6" t="n"/>
@@ -15897,6 +17082,10 @@
       <x:c r="O294" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P294" t="str"/>
+      <x:c r="Q294" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="6" t="n"/>
@@ -15948,6 +17137,10 @@
       <x:c r="O295" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P295" t="str"/>
+      <x:c r="Q295" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="6" t="n"/>
@@ -15999,6 +17192,10 @@
       <x:c r="O296" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P296" t="str"/>
+      <x:c r="Q296" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="6" t="n"/>
@@ -16050,6 +17247,10 @@
       <x:c r="O297" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P297" t="str"/>
+      <x:c r="Q297" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="6" t="n"/>
@@ -16101,6 +17302,10 @@
       <x:c r="O298" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P298" t="str"/>
+      <x:c r="Q298" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="6" t="n"/>
@@ -16152,6 +17357,10 @@
       <x:c r="O299" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P299" t="str"/>
+      <x:c r="Q299" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="6" t="n"/>
@@ -16203,6 +17412,10 @@
       <x:c r="O300" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P300" t="str"/>
+      <x:c r="Q300" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="6" t="n"/>
@@ -16258,6 +17471,10 @@
       <x:c r="O301" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P301" t="str"/>
+      <x:c r="Q301" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="6" t="n"/>
@@ -16313,6 +17530,10 @@
       <x:c r="O302" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P302" t="str"/>
+      <x:c r="Q302" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="6" t="n"/>
@@ -16368,6 +17589,10 @@
       <x:c r="O303" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P303" t="str"/>
+      <x:c r="Q303" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="6" t="n"/>
@@ -16419,6 +17644,10 @@
       <x:c r="O304" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P304" t="str"/>
+      <x:c r="Q304" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="6" t="n"/>
@@ -16470,6 +17699,10 @@
       <x:c r="O305" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P305" t="str"/>
+      <x:c r="Q305" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="6" t="n"/>
@@ -16521,6 +17754,10 @@
       <x:c r="O306" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P306" t="str"/>
+      <x:c r="Q306" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="6" t="n"/>
@@ -16572,6 +17809,10 @@
       <x:c r="O307" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P307" t="str"/>
+      <x:c r="Q307" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="6" t="n"/>
@@ -16623,6 +17864,10 @@
       <x:c r="O308" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P308" t="str"/>
+      <x:c r="Q308" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="6" t="n"/>
@@ -16674,6 +17919,10 @@
       <x:c r="O309" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P309" t="str"/>
+      <x:c r="Q309" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="6" t="n"/>
@@ -16725,6 +17974,10 @@
       <x:c r="O310" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P310" t="str"/>
+      <x:c r="Q310" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="6" t="n"/>
@@ -16776,6 +18029,10 @@
       <x:c r="O311" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P311" t="str"/>
+      <x:c r="Q311" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="6" t="n"/>
@@ -16827,6 +18084,10 @@
       <x:c r="O312" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P312" t="str"/>
+      <x:c r="Q312" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="6" t="n"/>
@@ -16878,6 +18139,10 @@
       <x:c r="O313" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P313" t="str"/>
+      <x:c r="Q313" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="6" t="n"/>
@@ -16929,6 +18194,10 @@
       <x:c r="O314" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P314" t="str"/>
+      <x:c r="Q314" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="6" t="n"/>
@@ -16984,6 +18253,10 @@
       <x:c r="O315" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P315" t="str"/>
+      <x:c r="Q315" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="6" t="n"/>
@@ -17039,6 +18312,10 @@
       <x:c r="O316" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P316" t="str"/>
+      <x:c r="Q316" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="6" t="n"/>
@@ -17090,6 +18367,10 @@
       <x:c r="O317" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P317" t="str"/>
+      <x:c r="Q317" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="6" t="n"/>
@@ -17141,6 +18422,10 @@
       <x:c r="O318" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P318" t="str"/>
+      <x:c r="Q318" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="6" t="n"/>
@@ -17192,6 +18477,10 @@
       <x:c r="O319" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P319" t="str"/>
+      <x:c r="Q319" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="6" t="n"/>
@@ -17243,6 +18532,10 @@
       <x:c r="O320" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P320" t="str"/>
+      <x:c r="Q320" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="6" t="n"/>
@@ -17294,6 +18587,10 @@
       <x:c r="O321" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P321" t="str"/>
+      <x:c r="Q321" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="6" t="n"/>
@@ -17345,6 +18642,10 @@
       <x:c r="O322" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P322" t="str"/>
+      <x:c r="Q322" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="6" t="n"/>
@@ -17396,6 +18697,10 @@
       <x:c r="O323" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P323" t="str"/>
+      <x:c r="Q323" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="6" t="n"/>
@@ -17447,6 +18752,10 @@
       <x:c r="O324" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P324" t="str"/>
+      <x:c r="Q324" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="6" t="n"/>
@@ -17498,6 +18807,10 @@
       <x:c r="O325" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P325" t="str"/>
+      <x:c r="Q325" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="6" t="n"/>
@@ -17549,6 +18862,10 @@
       <x:c r="O326" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P326" t="str"/>
+      <x:c r="Q326" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="6" t="n"/>
@@ -17604,6 +18921,10 @@
       <x:c r="O327" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P327" t="str"/>
+      <x:c r="Q327" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="6" t="n"/>
@@ -17659,6 +18980,10 @@
       <x:c r="O328" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P328" t="str"/>
+      <x:c r="Q328" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="6" t="n"/>
@@ -17714,6 +19039,10 @@
       <x:c r="O329" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P329" t="str"/>
+      <x:c r="Q329" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="6" t="n"/>
@@ -17769,6 +19098,10 @@
       <x:c r="O330" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P330" t="str"/>
+      <x:c r="Q330" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="6" t="n"/>
@@ -17824,6 +19157,10 @@
       <x:c r="O331" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P331" t="str"/>
+      <x:c r="Q331" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="6" t="n"/>
@@ -17879,6 +19216,10 @@
       <x:c r="O332" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P332" t="str"/>
+      <x:c r="Q332" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="6" t="n"/>
@@ -17934,6 +19275,10 @@
       <x:c r="O333" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P333" t="str"/>
+      <x:c r="Q333" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="6" t="n"/>
@@ -17989,6 +19334,10 @@
       <x:c r="O334" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P334" t="str"/>
+      <x:c r="Q334" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="6" t="n"/>
@@ -18044,6 +19393,10 @@
       <x:c r="O335" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P335" t="str"/>
+      <x:c r="Q335" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="6" t="n"/>
@@ -18099,6 +19452,10 @@
       <x:c r="O336" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P336" t="str"/>
+      <x:c r="Q336" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="6" t="n"/>
@@ -18154,6 +19511,10 @@
       <x:c r="O337" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P337" t="str"/>
+      <x:c r="Q337" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="6" t="n"/>
@@ -18209,6 +19570,10 @@
       <x:c r="O338" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P338" t="str"/>
+      <x:c r="Q338" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="6" t="n"/>
@@ -18264,6 +19629,10 @@
       <x:c r="O339" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P339" t="str"/>
+      <x:c r="Q339" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="6" t="n"/>
@@ -18319,6 +19688,10 @@
       <x:c r="O340" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P340" t="str"/>
+      <x:c r="Q340" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="6" t="n"/>
@@ -18374,6 +19747,10 @@
       <x:c r="O341" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P341" t="str"/>
+      <x:c r="Q341" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="6" t="n"/>
@@ -18429,6 +19806,10 @@
       <x:c r="O342" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P342" t="str"/>
+      <x:c r="Q342" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="6" t="n"/>
@@ -18484,6 +19865,10 @@
       <x:c r="O343" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P343" t="str"/>
+      <x:c r="Q343" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="6" t="n"/>
@@ -18539,6 +19924,10 @@
       <x:c r="O344" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P344" t="str"/>
+      <x:c r="Q344" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="6" t="n"/>
@@ -18594,6 +19983,10 @@
       <x:c r="O345" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P345" t="str"/>
+      <x:c r="Q345" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="6" t="n"/>
@@ -18649,6 +20042,10 @@
       <x:c r="O346" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P346" t="str"/>
+      <x:c r="Q346" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="6" t="n"/>
@@ -18704,6 +20101,10 @@
       <x:c r="O347" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P347" t="str"/>
+      <x:c r="Q347" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="6" t="n"/>
@@ -18759,6 +20160,10 @@
       <x:c r="O348" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P348" t="str"/>
+      <x:c r="Q348" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="6" t="n"/>
@@ -18810,6 +20215,10 @@
       <x:c r="O349" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P349" t="str"/>
+      <x:c r="Q349" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="6" t="n"/>
@@ -18861,6 +20270,10 @@
       <x:c r="O350" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P350" t="str"/>
+      <x:c r="Q350" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="6" t="n"/>
@@ -18912,6 +20325,10 @@
       <x:c r="O351" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P351" t="str"/>
+      <x:c r="Q351" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="6" t="n"/>
@@ -18963,6 +20380,10 @@
       <x:c r="O352" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P352" t="str"/>
+      <x:c r="Q352" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="6" t="n"/>
@@ -19014,6 +20435,10 @@
       <x:c r="O353" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P353" t="str"/>
+      <x:c r="Q353" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="6" t="n"/>
@@ -19065,6 +20490,10 @@
       <x:c r="O354" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P354" t="str"/>
+      <x:c r="Q354" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="6" t="n"/>
@@ -19116,6 +20545,10 @@
       <x:c r="O355" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P355" t="str"/>
+      <x:c r="Q355" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="6" t="n"/>
@@ -19167,6 +20600,10 @@
       <x:c r="O356" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P356" t="str"/>
+      <x:c r="Q356" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="6" t="n"/>
@@ -19218,6 +20655,10 @@
       <x:c r="O357" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P357" t="str"/>
+      <x:c r="Q357" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="6" t="n"/>
@@ -19269,6 +20710,10 @@
       <x:c r="O358" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P358" t="str"/>
+      <x:c r="Q358" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="6" t="n"/>
@@ -19320,6 +20765,10 @@
       <x:c r="O359" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P359" t="str"/>
+      <x:c r="Q359" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="6" t="n"/>
@@ -19371,6 +20820,10 @@
       <x:c r="O360" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P360" t="str"/>
+      <x:c r="Q360" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="6" t="n"/>
@@ -19422,6 +20875,10 @@
       <x:c r="O361" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P361" t="str"/>
+      <x:c r="Q361" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="6" t="n"/>
@@ -19473,6 +20930,10 @@
       <x:c r="O362" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P362" t="str"/>
+      <x:c r="Q362" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="6" t="n"/>
@@ -19524,6 +20985,10 @@
       <x:c r="O363" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P363" t="str"/>
+      <x:c r="Q363" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="6" t="n"/>
@@ -19575,6 +21040,10 @@
       <x:c r="O364" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P364" t="str"/>
+      <x:c r="Q364" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="6" t="n"/>
@@ -19626,6 +21095,10 @@
       <x:c r="O365" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P365" t="str"/>
+      <x:c r="Q365" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="6" t="n"/>
@@ -19677,6 +21150,10 @@
       <x:c r="O366" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P366" t="str"/>
+      <x:c r="Q366" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="6" t="n"/>
@@ -19728,6 +21205,10 @@
       <x:c r="O367" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P367" t="str"/>
+      <x:c r="Q367" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="6" t="n"/>
@@ -19779,6 +21260,10 @@
       <x:c r="O368" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P368" t="str"/>
+      <x:c r="Q368" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="6" t="n"/>
@@ -19830,6 +21315,10 @@
       <x:c r="O369" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P369" t="str"/>
+      <x:c r="Q369" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="6" t="n"/>
@@ -19881,6 +21370,10 @@
       <x:c r="O370" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P370" t="str"/>
+      <x:c r="Q370" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="6" t="n"/>
@@ -19932,6 +21425,10 @@
       <x:c r="O371" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P371" t="str"/>
+      <x:c r="Q371" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="6" t="n"/>
@@ -19983,6 +21480,10 @@
       <x:c r="O372" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P372" t="str"/>
+      <x:c r="Q372" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="6" t="n"/>
@@ -20034,6 +21535,10 @@
       <x:c r="O373" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P373" t="str"/>
+      <x:c r="Q373" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="6" t="n"/>
@@ -20085,6 +21590,10 @@
       <x:c r="O374" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P374" t="str"/>
+      <x:c r="Q374" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="6" t="n"/>
@@ -20136,6 +21645,10 @@
       <x:c r="O375" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P375" t="str"/>
+      <x:c r="Q375" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="6" t="n"/>
@@ -20187,6 +21700,10 @@
       <x:c r="O376" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P376" t="str"/>
+      <x:c r="Q376" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="6" t="n"/>
@@ -20238,6 +21755,10 @@
       <x:c r="O377" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P377" t="str"/>
+      <x:c r="Q377" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="6" t="n"/>
@@ -20289,6 +21810,10 @@
       <x:c r="O378" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P378" t="str"/>
+      <x:c r="Q378" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="6" t="n"/>
@@ -20340,6 +21865,10 @@
       <x:c r="O379" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P379" t="str"/>
+      <x:c r="Q379" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="6" t="n"/>
@@ -20395,6 +21924,10 @@
       <x:c r="O380" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P380" t="str"/>
+      <x:c r="Q380" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="6" t="n"/>
@@ -20450,6 +21983,10 @@
       <x:c r="O381" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P381" t="str"/>
+      <x:c r="Q381" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="6" t="n"/>
@@ -20505,6 +22042,10 @@
       <x:c r="O382" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P382" t="str"/>
+      <x:c r="Q382" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="6" t="n"/>
@@ -20556,6 +22097,10 @@
       <x:c r="O383" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P383" t="str"/>
+      <x:c r="Q383" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="6" t="n"/>
@@ -20607,6 +22152,10 @@
       <x:c r="O384" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P384" t="str"/>
+      <x:c r="Q384" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="6" t="n"/>
@@ -20658,6 +22207,10 @@
       <x:c r="O385" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P385" t="str"/>
+      <x:c r="Q385" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="6" t="n"/>
@@ -20709,6 +22262,10 @@
       <x:c r="O386" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P386" t="str"/>
+      <x:c r="Q386" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="6" t="n"/>
@@ -20760,6 +22317,10 @@
       <x:c r="O387" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P387" t="str"/>
+      <x:c r="Q387" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="6" t="n"/>
@@ -20811,6 +22372,10 @@
       <x:c r="O388" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P388" t="str"/>
+      <x:c r="Q388" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="6" t="n"/>
@@ -20862,6 +22427,10 @@
       <x:c r="O389" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P389" t="str"/>
+      <x:c r="Q389" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="6" t="n"/>
@@ -20913,6 +22482,10 @@
       <x:c r="O390" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P390" t="str"/>
+      <x:c r="Q390" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="6" t="n"/>
@@ -20964,6 +22537,10 @@
       <x:c r="O391" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P391" t="str"/>
+      <x:c r="Q391" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="6" t="n"/>
@@ -21015,6 +22592,10 @@
       <x:c r="O392" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P392" t="str"/>
+      <x:c r="Q392" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="6" t="n"/>
@@ -21066,6 +22647,10 @@
       <x:c r="O393" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P393" t="str"/>
+      <x:c r="Q393" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="6" t="n"/>
@@ -21121,6 +22706,10 @@
       <x:c r="O394" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P394" t="str"/>
+      <x:c r="Q394" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="6" t="n"/>
@@ -21176,6 +22765,10 @@
       <x:c r="O395" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P395" t="str"/>
+      <x:c r="Q395" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="6" t="n"/>
@@ -21227,6 +22820,10 @@
       <x:c r="O396" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P396" t="str"/>
+      <x:c r="Q396" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="6" t="n"/>
@@ -21278,6 +22875,10 @@
       <x:c r="O397" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P397" t="str"/>
+      <x:c r="Q397" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="6" t="n"/>
@@ -21329,6 +22930,10 @@
       <x:c r="O398" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P398" t="str"/>
+      <x:c r="Q398" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="6" t="n"/>
@@ -21380,6 +22985,10 @@
       <x:c r="O399" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P399" t="str"/>
+      <x:c r="Q399" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="6" t="n"/>
@@ -21431,6 +23040,10 @@
       <x:c r="O400" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P400" t="str"/>
+      <x:c r="Q400" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="6" t="n"/>
@@ -21482,6 +23095,10 @@
       <x:c r="O401" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P401" t="str"/>
+      <x:c r="Q401" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="6" t="n"/>
@@ -21533,6 +23150,10 @@
       <x:c r="O402" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P402" t="str"/>
+      <x:c r="Q402" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="6" t="n"/>
@@ -21584,6 +23205,10 @@
       <x:c r="O403" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P403" t="str"/>
+      <x:c r="Q403" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="6" t="n"/>
@@ -21635,6 +23260,10 @@
       <x:c r="O404" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P404" t="str"/>
+      <x:c r="Q404" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="6" t="n"/>
@@ -21686,6 +23315,10 @@
       <x:c r="O405" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P405" t="str"/>
+      <x:c r="Q405" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="6" t="n"/>
@@ -21741,6 +23374,10 @@
       <x:c r="O406" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P406" t="str"/>
+      <x:c r="Q406" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="6" t="n"/>
@@ -21796,6 +23433,10 @@
       <x:c r="O407" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P407" t="str"/>
+      <x:c r="Q407" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="6" t="n"/>
@@ -21851,6 +23492,10 @@
       <x:c r="O408" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P408" t="str"/>
+      <x:c r="Q408" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="6" t="n"/>
@@ -21906,6 +23551,10 @@
       <x:c r="O409" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P409" t="str"/>
+      <x:c r="Q409" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="6" t="n"/>
@@ -21961,6 +23610,10 @@
       <x:c r="O410" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P410" t="str"/>
+      <x:c r="Q410" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="6" t="n"/>
@@ -22016,6 +23669,10 @@
       <x:c r="O411" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P411" t="str"/>
+      <x:c r="Q411" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="6" t="n"/>
@@ -22071,6 +23728,10 @@
       <x:c r="O412" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P412" t="str"/>
+      <x:c r="Q412" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="6" t="n"/>
@@ -22126,6 +23787,10 @@
       <x:c r="O413" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P413" t="str"/>
+      <x:c r="Q413" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="6" t="n"/>
@@ -22181,6 +23846,10 @@
       <x:c r="O414" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P414" t="str"/>
+      <x:c r="Q414" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="6" t="n"/>
@@ -22236,6 +23905,10 @@
       <x:c r="O415" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P415" t="str"/>
+      <x:c r="Q415" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="6" t="n"/>
@@ -22291,6 +23964,10 @@
       <x:c r="O416" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P416" t="str"/>
+      <x:c r="Q416" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="6" t="n"/>
@@ -22346,6 +24023,10 @@
       <x:c r="O417" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P417" t="str"/>
+      <x:c r="Q417" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="6" t="n"/>
@@ -22401,6 +24082,10 @@
       <x:c r="O418" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P418" t="str"/>
+      <x:c r="Q418" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="6" t="n"/>
@@ -22456,6 +24141,10 @@
       <x:c r="O419" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P419" t="str"/>
+      <x:c r="Q419" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="6" t="n"/>
@@ -22511,6 +24200,10 @@
       <x:c r="O420" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P420" t="str"/>
+      <x:c r="Q420" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="6" t="n"/>
@@ -22566,6 +24259,10 @@
       <x:c r="O421" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P421" t="str"/>
+      <x:c r="Q421" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="6" t="n"/>
@@ -22621,6 +24318,10 @@
       <x:c r="O422" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P422" t="str"/>
+      <x:c r="Q422" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="6" t="n"/>
@@ -22676,6 +24377,10 @@
       <x:c r="O423" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P423" t="str"/>
+      <x:c r="Q423" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="6" t="n"/>
@@ -22731,6 +24436,10 @@
       <x:c r="O424" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P424" t="str"/>
+      <x:c r="Q424" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="6" t="n"/>
@@ -22786,6 +24495,10 @@
       <x:c r="O425" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P425" t="str"/>
+      <x:c r="Q425" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="6" t="n"/>
@@ -22841,6 +24554,10 @@
       <x:c r="O426" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P426" t="str"/>
+      <x:c r="Q426" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="6" t="n"/>
@@ -22896,6 +24613,10 @@
       <x:c r="O427" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P427" t="str"/>
+      <x:c r="Q427" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="6" t="n"/>
@@ -22947,6 +24668,10 @@
       <x:c r="O428" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P428" t="str"/>
+      <x:c r="Q428" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="6" t="n"/>
@@ -22998,6 +24723,10 @@
       <x:c r="O429" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P429" t="str"/>
+      <x:c r="Q429" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="6" t="n"/>
@@ -23049,6 +24778,10 @@
       <x:c r="O430" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P430" t="str"/>
+      <x:c r="Q430" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="6" t="n"/>
@@ -23100,6 +24833,10 @@
       <x:c r="O431" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P431" t="str"/>
+      <x:c r="Q431" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="6" t="n"/>
@@ -23151,6 +24888,10 @@
       <x:c r="O432" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P432" t="str"/>
+      <x:c r="Q432" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="6" t="n"/>
@@ -23202,6 +24943,10 @@
       <x:c r="O433" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P433" t="str"/>
+      <x:c r="Q433" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="6" t="n"/>
@@ -23253,6 +24998,10 @@
       <x:c r="O434" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P434" t="str"/>
+      <x:c r="Q434" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="6" t="n"/>
@@ -23304,6 +25053,10 @@
       <x:c r="O435" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P435" t="str"/>
+      <x:c r="Q435" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="6" t="n"/>
@@ -23355,6 +25108,10 @@
       <x:c r="O436" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P436" t="str"/>
+      <x:c r="Q436" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="6" t="n"/>
@@ -23406,6 +25163,10 @@
       <x:c r="O437" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P437" t="str"/>
+      <x:c r="Q437" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="6" t="n"/>
@@ -23457,6 +25218,10 @@
       <x:c r="O438" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P438" t="str"/>
+      <x:c r="Q438" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="6" t="n"/>
@@ -23508,6 +25273,10 @@
       <x:c r="O439" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P439" t="str"/>
+      <x:c r="Q439" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="6" t="n"/>
@@ -23559,6 +25328,10 @@
       <x:c r="O440" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P440" t="str"/>
+      <x:c r="Q440" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="6" t="n"/>
@@ -23610,6 +25383,10 @@
       <x:c r="O441" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P441" t="str"/>
+      <x:c r="Q441" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="6" t="n"/>
@@ -23661,6 +25438,10 @@
       <x:c r="O442" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P442" t="str"/>
+      <x:c r="Q442" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="6" t="n"/>
@@ -23712,6 +25493,10 @@
       <x:c r="O443" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P443" t="str"/>
+      <x:c r="Q443" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="6" t="n"/>
@@ -23763,6 +25548,10 @@
       <x:c r="O444" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P444" t="str"/>
+      <x:c r="Q444" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="6" t="n"/>
@@ -23814,6 +25603,10 @@
       <x:c r="O445" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P445" t="str"/>
+      <x:c r="Q445" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="6" t="n"/>
@@ -23865,6 +25658,10 @@
       <x:c r="O446" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P446" t="str"/>
+      <x:c r="Q446" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="6" t="n"/>
@@ -23916,6 +25713,10 @@
       <x:c r="O447" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P447" t="str"/>
+      <x:c r="Q447" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="6" t="n"/>
@@ -23967,6 +25768,10 @@
       <x:c r="O448" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P448" t="str"/>
+      <x:c r="Q448" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="6" t="n"/>
@@ -24018,6 +25823,10 @@
       <x:c r="O449" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P449" t="str"/>
+      <x:c r="Q449" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="6" t="n"/>
@@ -24069,6 +25878,10 @@
       <x:c r="O450" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P450" t="str"/>
+      <x:c r="Q450" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="6" t="n"/>
@@ -24120,6 +25933,10 @@
       <x:c r="O451" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P451" t="str"/>
+      <x:c r="Q451" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="6" t="n"/>
@@ -24171,6 +25988,10 @@
       <x:c r="O452" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P452" t="str"/>
+      <x:c r="Q452" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="6" t="n"/>
@@ -24222,6 +26043,10 @@
       <x:c r="O453" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P453" t="str"/>
+      <x:c r="Q453" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="6" t="n"/>
@@ -24273,6 +26098,10 @@
       <x:c r="O454" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P454" t="str"/>
+      <x:c r="Q454" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="6" t="n"/>
@@ -24324,6 +26153,10 @@
       <x:c r="O455" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P455" t="str"/>
+      <x:c r="Q455" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="6" t="n"/>
@@ -24375,6 +26208,10 @@
       <x:c r="O456" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P456" t="str"/>
+      <x:c r="Q456" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="6" t="n"/>
@@ -24426,6 +26263,10 @@
       <x:c r="O457" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P457" t="str"/>
+      <x:c r="Q457" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="6" t="n"/>
@@ -24477,6 +26318,10 @@
       <x:c r="O458" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P458" t="str"/>
+      <x:c r="Q458" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="6" t="n"/>
@@ -24532,6 +26377,10 @@
       <x:c r="O459" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P459" t="str"/>
+      <x:c r="Q459" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="6" t="n"/>
@@ -24587,6 +26436,10 @@
       <x:c r="O460" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P460" t="str"/>
+      <x:c r="Q460" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="6" t="n"/>
@@ -24642,6 +26495,10 @@
       <x:c r="O461" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P461" t="str"/>
+      <x:c r="Q461" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="6" t="n"/>
@@ -24693,6 +26550,10 @@
       <x:c r="O462" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P462" t="str"/>
+      <x:c r="Q462" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="6" t="n"/>
@@ -24744,6 +26605,10 @@
       <x:c r="O463" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P463" t="str"/>
+      <x:c r="Q463" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="6" t="n"/>
@@ -24795,6 +26660,10 @@
       <x:c r="O464" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P464" t="str"/>
+      <x:c r="Q464" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="6" t="n"/>
@@ -24846,6 +26715,10 @@
       <x:c r="O465" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P465" t="str"/>
+      <x:c r="Q465" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="6" t="n"/>
@@ -24897,6 +26770,10 @@
       <x:c r="O466" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P466" t="str"/>
+      <x:c r="Q466" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="6" t="n"/>
@@ -24948,6 +26825,10 @@
       <x:c r="O467" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P467" t="str"/>
+      <x:c r="Q467" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="6" t="n"/>
@@ -24999,6 +26880,10 @@
       <x:c r="O468" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P468" t="str"/>
+      <x:c r="Q468" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="6" t="n"/>
@@ -25050,6 +26935,10 @@
       <x:c r="O469" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P469" t="str"/>
+      <x:c r="Q469" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="6" t="n"/>
@@ -25101,6 +26990,10 @@
       <x:c r="O470" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P470" t="str"/>
+      <x:c r="Q470" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="6" t="n"/>
@@ -25152,6 +27045,10 @@
       <x:c r="O471" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P471" t="str"/>
+      <x:c r="Q471" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="6" t="n"/>
@@ -25203,6 +27100,10 @@
       <x:c r="O472" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P472" t="str"/>
+      <x:c r="Q472" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="6" t="n"/>
@@ -25258,6 +27159,10 @@
       <x:c r="O473" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P473" t="str"/>
+      <x:c r="Q473" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="6" t="n"/>
@@ -25313,6 +27218,10 @@
       <x:c r="O474" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P474" t="str"/>
+      <x:c r="Q474" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="6" t="n"/>
@@ -25364,6 +27273,10 @@
       <x:c r="O475" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P475" t="str"/>
+      <x:c r="Q475" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="6" t="n"/>
@@ -25415,6 +27328,10 @@
       <x:c r="O476" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P476" t="str"/>
+      <x:c r="Q476" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="6" t="n"/>
@@ -25466,6 +27383,10 @@
       <x:c r="O477" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P477" t="str"/>
+      <x:c r="Q477" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="6" t="n"/>
@@ -25517,6 +27438,10 @@
       <x:c r="O478" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P478" t="str"/>
+      <x:c r="Q478" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="6" t="n"/>
@@ -25568,6 +27493,10 @@
       <x:c r="O479" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P479" t="str"/>
+      <x:c r="Q479" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="6" t="n"/>
@@ -25619,6 +27548,10 @@
       <x:c r="O480" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P480" t="str"/>
+      <x:c r="Q480" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="6" t="n"/>
@@ -25670,6 +27603,10 @@
       <x:c r="O481" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P481" t="str"/>
+      <x:c r="Q481" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="6" t="n"/>
@@ -25721,6 +27658,10 @@
       <x:c r="O482" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P482" t="str"/>
+      <x:c r="Q482" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="6" t="n"/>
@@ -25772,6 +27713,10 @@
       <x:c r="O483" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P483" t="str"/>
+      <x:c r="Q483" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="6" t="n"/>
@@ -25823,6 +27768,10 @@
       <x:c r="O484" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P484" t="str"/>
+      <x:c r="Q484" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="6" t="n"/>
@@ -25878,6 +27827,10 @@
       <x:c r="O485" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P485" t="str"/>
+      <x:c r="Q485" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="6" t="n"/>
@@ -25933,6 +27886,10 @@
       <x:c r="O486" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P486" t="str"/>
+      <x:c r="Q486" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="6" t="n"/>
@@ -25988,6 +27945,10 @@
       <x:c r="O487" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P487" t="str"/>
+      <x:c r="Q487" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="6" t="n"/>
@@ -26043,6 +28004,10 @@
       <x:c r="O488" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P488" t="str"/>
+      <x:c r="Q488" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="6" t="n"/>
@@ -26098,6 +28063,10 @@
       <x:c r="O489" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P489" t="str"/>
+      <x:c r="Q489" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="6" t="n"/>
@@ -26153,6 +28122,10 @@
       <x:c r="O490" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P490" t="str"/>
+      <x:c r="Q490" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="6" t="n"/>
@@ -26208,6 +28181,10 @@
       <x:c r="O491" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P491" t="str"/>
+      <x:c r="Q491" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="6" t="n"/>
@@ -26263,6 +28240,10 @@
       <x:c r="O492" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P492" t="str"/>
+      <x:c r="Q492" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="6" t="n"/>
@@ -26318,6 +28299,10 @@
       <x:c r="O493" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P493" t="str"/>
+      <x:c r="Q493" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="6" t="n"/>
@@ -26373,6 +28358,10 @@
       <x:c r="O494" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P494" t="str"/>
+      <x:c r="Q494" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="6" t="n"/>
@@ -26428,6 +28417,10 @@
       <x:c r="O495" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P495" t="str"/>
+      <x:c r="Q495" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="6" t="n"/>
@@ -26483,6 +28476,10 @@
       <x:c r="O496" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P496" t="str"/>
+      <x:c r="Q496" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="6" t="n"/>
@@ -26538,6 +28535,10 @@
       <x:c r="O497" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P497" t="str"/>
+      <x:c r="Q497" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="6" t="n"/>
@@ -26593,6 +28594,10 @@
       <x:c r="O498" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P498" t="str"/>
+      <x:c r="Q498" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="6" t="n"/>
@@ -26648,6 +28653,10 @@
       <x:c r="O499" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P499" t="str"/>
+      <x:c r="Q499" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="6" t="n"/>
@@ -26703,6 +28712,10 @@
       <x:c r="O500" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P500" t="str"/>
+      <x:c r="Q500" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="501">
       <x:c r="A501" s="6" t="n"/>
@@ -26758,6 +28771,10 @@
       <x:c r="O501" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P501" t="str"/>
+      <x:c r="Q501" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="502">
       <x:c r="A502" s="6" t="n"/>
@@ -26813,6 +28830,10 @@
       <x:c r="O502" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P502" t="str"/>
+      <x:c r="Q502" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="503">
       <x:c r="A503" s="6" t="n"/>
@@ -26868,6 +28889,10 @@
       <x:c r="O503" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P503" t="str"/>
+      <x:c r="Q503" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="504">
       <x:c r="A504" s="6" t="n"/>
@@ -26923,6 +28948,10 @@
       <x:c r="O504" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P504" t="str"/>
+      <x:c r="Q504" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="505">
       <x:c r="A505" s="6" t="n"/>
@@ -26978,6 +29007,10 @@
       <x:c r="O505" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P505" t="str"/>
+      <x:c r="Q505" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="6" t="n"/>
@@ -27033,6 +29066,10 @@
       <x:c r="O506" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P506" t="str"/>
+      <x:c r="Q506" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="507">
       <x:c r="A507" s="6" t="n"/>
@@ -27084,6 +29121,10 @@
       <x:c r="O507" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P507" t="str"/>
+      <x:c r="Q507" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="508">
       <x:c r="A508" s="6" t="n"/>
@@ -27135,6 +29176,10 @@
       <x:c r="O508" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P508" t="str"/>
+      <x:c r="Q508" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="509">
       <x:c r="A509" s="6" t="n"/>
@@ -27186,6 +29231,10 @@
       <x:c r="O509" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P509" t="str"/>
+      <x:c r="Q509" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="510">
       <x:c r="A510" s="6" t="n"/>
@@ -27237,6 +29286,10 @@
       <x:c r="O510" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P510" t="str"/>
+      <x:c r="Q510" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="511">
       <x:c r="A511" s="6" t="n"/>
@@ -27288,6 +29341,10 @@
       <x:c r="O511" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P511" t="str"/>
+      <x:c r="Q511" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="512">
       <x:c r="A512" s="6" t="n"/>
@@ -27339,6 +29396,10 @@
       <x:c r="O512" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P512" t="str"/>
+      <x:c r="Q512" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="513">
       <x:c r="A513" s="6" t="n"/>
@@ -27390,6 +29451,10 @@
       <x:c r="O513" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P513" t="str"/>
+      <x:c r="Q513" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="514">
       <x:c r="A514" s="6" t="n"/>
@@ -27441,6 +29506,10 @@
       <x:c r="O514" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P514" t="str"/>
+      <x:c r="Q514" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="6" t="n"/>
@@ -27492,6 +29561,10 @@
       <x:c r="O515" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P515" t="str"/>
+      <x:c r="Q515" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="516">
       <x:c r="A516" s="6" t="n"/>
@@ -27543,6 +29616,10 @@
       <x:c r="O516" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P516" t="str"/>
+      <x:c r="Q516" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="517">
       <x:c r="A517" s="6" t="n"/>
@@ -27594,6 +29671,10 @@
       <x:c r="O517" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P517" t="str"/>
+      <x:c r="Q517" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="518">
       <x:c r="A518" s="6" t="n"/>
@@ -27645,6 +29726,10 @@
       <x:c r="O518" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P518" t="str"/>
+      <x:c r="Q518" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="519">
       <x:c r="A519" s="6" t="n"/>
@@ -27696,6 +29781,10 @@
       <x:c r="O519" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P519" t="str"/>
+      <x:c r="Q519" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="520">
       <x:c r="A520" s="6" t="n"/>
@@ -27747,6 +29836,10 @@
       <x:c r="O520" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P520" t="str"/>
+      <x:c r="Q520" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="521">
       <x:c r="A521" s="6" t="n"/>
@@ -27798,6 +29891,10 @@
       <x:c r="O521" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P521" t="str"/>
+      <x:c r="Q521" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="522">
       <x:c r="A522" s="6" t="n"/>
@@ -27849,6 +29946,10 @@
       <x:c r="O522" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P522" t="str"/>
+      <x:c r="Q522" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="523">
       <x:c r="A523" s="6" t="n"/>
@@ -27900,6 +30001,10 @@
       <x:c r="O523" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P523" t="str"/>
+      <x:c r="Q523" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="524">
       <x:c r="A524" s="6" t="n"/>
@@ -27951,6 +30056,10 @@
       <x:c r="O524" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P524" t="str"/>
+      <x:c r="Q524" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="525">
       <x:c r="A525" s="6" t="n"/>
@@ -28002,6 +30111,10 @@
       <x:c r="O525" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P525" t="str"/>
+      <x:c r="Q525" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="526">
       <x:c r="A526" s="6" t="n"/>
@@ -28053,6 +30166,10 @@
       <x:c r="O526" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P526" t="str"/>
+      <x:c r="Q526" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="527">
       <x:c r="A527" s="6" t="n"/>
@@ -28104,6 +30221,10 @@
       <x:c r="O527" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P527" t="str"/>
+      <x:c r="Q527" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="528">
       <x:c r="A528" s="6" t="n"/>
@@ -28155,6 +30276,10 @@
       <x:c r="O528" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P528" t="str"/>
+      <x:c r="Q528" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="529">
       <x:c r="A529" s="6" t="n"/>
@@ -28206,6 +30331,10 @@
       <x:c r="O529" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P529" t="str"/>
+      <x:c r="Q529" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="530">
       <x:c r="A530" s="6" t="n"/>
@@ -28257,6 +30386,10 @@
       <x:c r="O530" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P530" t="str"/>
+      <x:c r="Q530" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="531">
       <x:c r="A531" s="6" t="n"/>
@@ -28308,6 +30441,10 @@
       <x:c r="O531" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P531" t="str"/>
+      <x:c r="Q531" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="532">
       <x:c r="A532" s="6" t="n"/>
@@ -28359,6 +30496,10 @@
       <x:c r="O532" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P532" t="str"/>
+      <x:c r="Q532" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="533">
       <x:c r="A533" s="6" t="n"/>
@@ -28410,6 +30551,10 @@
       <x:c r="O533" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P533" t="str"/>
+      <x:c r="Q533" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="534">
       <x:c r="A534" s="6" t="n"/>
@@ -28461,6 +30606,10 @@
       <x:c r="O534" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P534" t="str"/>
+      <x:c r="Q534" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="535">
       <x:c r="A535" s="6" t="n"/>
@@ -28512,6 +30661,10 @@
       <x:c r="O535" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P535" t="str"/>
+      <x:c r="Q535" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="536">
       <x:c r="A536" s="6" t="n"/>
@@ -28563,6 +30716,10 @@
       <x:c r="O536" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P536" t="str"/>
+      <x:c r="Q536" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="537">
       <x:c r="A537" s="6" t="n"/>
@@ -28614,6 +30771,10 @@
       <x:c r="O537" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P537" t="str"/>
+      <x:c r="Q537" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="538">
       <x:c r="A538" s="6" t="n"/>
@@ -28669,6 +30830,10 @@
       <x:c r="O538" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P538" t="str"/>
+      <x:c r="Q538" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="539">
       <x:c r="A539" s="6" t="n"/>
@@ -28724,6 +30889,10 @@
       <x:c r="O539" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P539" t="str"/>
+      <x:c r="Q539" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="540">
       <x:c r="A540" s="6" t="n"/>
@@ -28779,6 +30948,10 @@
       <x:c r="O540" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P540" t="str"/>
+      <x:c r="Q540" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="541">
       <x:c r="A541" s="6" t="n"/>
@@ -28830,6 +31003,10 @@
       <x:c r="O541" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P541" t="str"/>
+      <x:c r="Q541" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="542">
       <x:c r="A542" s="6" t="n"/>
@@ -28881,6 +31058,10 @@
       <x:c r="O542" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P542" t="str"/>
+      <x:c r="Q542" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="543">
       <x:c r="A543" s="6" t="n"/>
@@ -28932,6 +31113,10 @@
       <x:c r="O543" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P543" t="str"/>
+      <x:c r="Q543" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="544">
       <x:c r="A544" s="6" t="n"/>
@@ -28983,6 +31168,10 @@
       <x:c r="O544" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P544" t="str"/>
+      <x:c r="Q544" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="545">
       <x:c r="A545" s="6" t="n"/>
@@ -29034,6 +31223,10 @@
       <x:c r="O545" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P545" t="str"/>
+      <x:c r="Q545" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="546">
       <x:c r="A546" s="6" t="n"/>
@@ -29085,6 +31278,10 @@
       <x:c r="O546" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P546" t="str"/>
+      <x:c r="Q546" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="547">
       <x:c r="A547" s="6" t="n"/>
@@ -29136,6 +31333,10 @@
       <x:c r="O547" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P547" t="str"/>
+      <x:c r="Q547" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="548">
       <x:c r="A548" s="6" t="n"/>
@@ -29187,6 +31388,10 @@
       <x:c r="O548" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P548" t="str"/>
+      <x:c r="Q548" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="549">
       <x:c r="A549" s="6" t="n"/>
@@ -29238,6 +31443,10 @@
       <x:c r="O549" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P549" t="str"/>
+      <x:c r="Q549" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="550">
       <x:c r="A550" s="6" t="n"/>
@@ -29289,6 +31498,10 @@
       <x:c r="O550" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P550" t="str"/>
+      <x:c r="Q550" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="551">
       <x:c r="A551" s="6" t="n"/>
@@ -29340,6 +31553,10 @@
       <x:c r="O551" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P551" t="str"/>
+      <x:c r="Q551" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="552">
       <x:c r="A552" s="6" t="n"/>
@@ -29395,6 +31612,10 @@
       <x:c r="O552" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P552" t="str"/>
+      <x:c r="Q552" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="553">
       <x:c r="A553" s="6" t="n"/>
@@ -29450,6 +31671,10 @@
       <x:c r="O553" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P553" t="str"/>
+      <x:c r="Q553" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="554">
       <x:c r="A554" s="6" t="n"/>
@@ -29501,6 +31726,10 @@
       <x:c r="O554" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P554" t="str"/>
+      <x:c r="Q554" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="555">
       <x:c r="A555" s="6" t="n"/>
@@ -29552,6 +31781,10 @@
       <x:c r="O555" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P555" t="str"/>
+      <x:c r="Q555" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="556">
       <x:c r="A556" s="6" t="n"/>
@@ -29603,6 +31836,10 @@
       <x:c r="O556" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P556" t="str"/>
+      <x:c r="Q556" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="557">
       <x:c r="A557" s="6" t="n"/>
@@ -29654,6 +31891,10 @@
       <x:c r="O557" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P557" t="str"/>
+      <x:c r="Q557" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="558">
       <x:c r="A558" s="6" t="n"/>
@@ -29705,6 +31946,10 @@
       <x:c r="O558" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P558" t="str"/>
+      <x:c r="Q558" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="559">
       <x:c r="A559" s="6" t="n"/>
@@ -29756,6 +32001,10 @@
       <x:c r="O559" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P559" t="str"/>
+      <x:c r="Q559" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="560">
       <x:c r="A560" s="6" t="n"/>
@@ -29807,6 +32056,10 @@
       <x:c r="O560" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P560" t="str"/>
+      <x:c r="Q560" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="561">
       <x:c r="A561" s="6" t="n"/>
@@ -29858,6 +32111,10 @@
       <x:c r="O561" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P561" t="str"/>
+      <x:c r="Q561" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="562">
       <x:c r="A562" s="6" t="n"/>
@@ -29909,6 +32166,10 @@
       <x:c r="O562" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P562" t="str"/>
+      <x:c r="Q562" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="563">
       <x:c r="A563" s="6" t="n"/>
@@ -29960,6 +32221,10 @@
       <x:c r="O563" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P563" t="str"/>
+      <x:c r="Q563" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="564">
       <x:c r="A564" s="6" t="n"/>
@@ -30015,6 +32280,10 @@
       <x:c r="O564" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P564" t="str"/>
+      <x:c r="Q564" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="565">
       <x:c r="A565" s="6" t="n"/>
@@ -30070,6 +32339,10 @@
       <x:c r="O565" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P565" t="str"/>
+      <x:c r="Q565" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="566">
       <x:c r="A566" s="6" t="n"/>
@@ -30125,6 +32398,10 @@
       <x:c r="O566" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P566" t="str"/>
+      <x:c r="Q566" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="567">
       <x:c r="A567" s="6" t="n"/>
@@ -30180,6 +32457,10 @@
       <x:c r="O567" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P567" t="str"/>
+      <x:c r="Q567" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="568">
       <x:c r="A568" s="6" t="n"/>
@@ -30235,6 +32516,10 @@
       <x:c r="O568" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P568" t="str"/>
+      <x:c r="Q568" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="569">
       <x:c r="A569" s="6" t="n"/>
@@ -30290,6 +32575,10 @@
       <x:c r="O569" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P569" t="str"/>
+      <x:c r="Q569" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="570">
       <x:c r="A570" s="6" t="n"/>
@@ -30345,6 +32634,10 @@
       <x:c r="O570" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P570" t="str"/>
+      <x:c r="Q570" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="571">
       <x:c r="A571" s="6" t="n"/>
@@ -30400,6 +32693,10 @@
       <x:c r="O571" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P571" t="str"/>
+      <x:c r="Q571" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="572">
       <x:c r="A572" s="6" t="n"/>
@@ -30455,6 +32752,10 @@
       <x:c r="O572" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P572" t="str"/>
+      <x:c r="Q572" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="573">
       <x:c r="A573" s="6" t="n"/>
@@ -30510,6 +32811,10 @@
       <x:c r="O573" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P573" t="str"/>
+      <x:c r="Q573" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="574">
       <x:c r="A574" s="6" t="n"/>
@@ -30565,6 +32870,10 @@
       <x:c r="O574" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P574" t="str"/>
+      <x:c r="Q574" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="575">
       <x:c r="A575" s="6" t="n"/>
@@ -30620,6 +32929,10 @@
       <x:c r="O575" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P575" t="str"/>
+      <x:c r="Q575" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="576">
       <x:c r="A576" s="6" t="n"/>
@@ -30675,6 +32988,10 @@
       <x:c r="O576" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P576" t="str"/>
+      <x:c r="Q576" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="577">
       <x:c r="A577" s="6" t="n"/>
@@ -30730,6 +33047,10 @@
       <x:c r="O577" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P577" t="str"/>
+      <x:c r="Q577" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="578">
       <x:c r="A578" s="6" t="n"/>
@@ -30785,6 +33106,10 @@
       <x:c r="O578" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P578" t="str"/>
+      <x:c r="Q578" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="579">
       <x:c r="A579" s="6" t="n"/>
@@ -30840,6 +33165,10 @@
       <x:c r="O579" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P579" t="str"/>
+      <x:c r="Q579" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="580">
       <x:c r="A580" s="6" t="n"/>
@@ -30895,6 +33224,10 @@
       <x:c r="O580" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P580" t="str"/>
+      <x:c r="Q580" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="581">
       <x:c r="A581" s="6" t="n"/>
@@ -30950,6 +33283,10 @@
       <x:c r="O581" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P581" t="str"/>
+      <x:c r="Q581" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="582">
       <x:c r="A582" s="6" t="n"/>
@@ -31005,6 +33342,10 @@
       <x:c r="O582" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P582" t="str"/>
+      <x:c r="Q582" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="583">
       <x:c r="A583" s="6" t="n"/>
@@ -31060,6 +33401,10 @@
       <x:c r="O583" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P583" t="str"/>
+      <x:c r="Q583" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="584">
       <x:c r="A584" s="6" t="n"/>
@@ -31115,6 +33460,10 @@
       <x:c r="O584" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P584" t="str"/>
+      <x:c r="Q584" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="585">
       <x:c r="A585" s="6" t="n"/>
@@ -31170,6 +33519,10 @@
       <x:c r="O585" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P585" t="str"/>
+      <x:c r="Q585" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="586">
       <x:c r="A586" s="6" t="n"/>
@@ -31221,6 +33574,10 @@
       <x:c r="O586" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P586" t="str"/>
+      <x:c r="Q586" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="587">
       <x:c r="A587" s="6" t="n"/>
@@ -31272,6 +33629,10 @@
       <x:c r="O587" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P587" t="str"/>
+      <x:c r="Q587" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="588">
       <x:c r="A588" s="6" t="n"/>
@@ -31323,6 +33684,10 @@
       <x:c r="O588" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P588" t="str"/>
+      <x:c r="Q588" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="589">
       <x:c r="A589" s="6" t="n"/>
@@ -31374,6 +33739,10 @@
       <x:c r="O589" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P589" t="str"/>
+      <x:c r="Q589" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="590">
       <x:c r="A590" s="6" t="n"/>
@@ -31425,6 +33794,10 @@
       <x:c r="O590" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P590" t="str"/>
+      <x:c r="Q590" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="591">
       <x:c r="A591" s="6" t="n"/>
@@ -31476,6 +33849,10 @@
       <x:c r="O591" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P591" t="str"/>
+      <x:c r="Q591" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="592">
       <x:c r="A592" s="6" t="n"/>
@@ -31527,6 +33904,10 @@
       <x:c r="O592" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P592" t="str"/>
+      <x:c r="Q592" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="593">
       <x:c r="A593" s="6" t="n"/>
@@ -31578,6 +33959,10 @@
       <x:c r="O593" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P593" t="str"/>
+      <x:c r="Q593" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="594">
       <x:c r="A594" s="6" t="n"/>
@@ -31629,6 +34014,10 @@
       <x:c r="O594" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P594" t="str"/>
+      <x:c r="Q594" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="595">
       <x:c r="A595" s="6" t="n"/>
@@ -31680,6 +34069,10 @@
       <x:c r="O595" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P595" t="str"/>
+      <x:c r="Q595" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="596">
       <x:c r="A596" s="6" t="n"/>
@@ -31731,6 +34124,10 @@
       <x:c r="O596" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P596" t="str"/>
+      <x:c r="Q596" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="597">
       <x:c r="A597" s="6" t="n"/>
@@ -31782,6 +34179,10 @@
       <x:c r="O597" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P597" t="str"/>
+      <x:c r="Q597" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="598">
       <x:c r="A598" s="6" t="n"/>
@@ -31833,6 +34234,10 @@
       <x:c r="O598" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P598" t="str"/>
+      <x:c r="Q598" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="599">
       <x:c r="A599" s="6" t="n"/>
@@ -31884,6 +34289,10 @@
       <x:c r="O599" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P599" t="str"/>
+      <x:c r="Q599" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="600">
       <x:c r="A600" s="6" t="n"/>
@@ -31935,6 +34344,10 @@
       <x:c r="O600" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P600" t="str"/>
+      <x:c r="Q600" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="601">
       <x:c r="A601" s="6" t="n"/>
@@ -31986,6 +34399,10 @@
       <x:c r="O601" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P601" t="str"/>
+      <x:c r="Q601" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="602">
       <x:c r="A602" s="6" t="n"/>
@@ -32037,6 +34454,10 @@
       <x:c r="O602" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P602" t="str"/>
+      <x:c r="Q602" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="603">
       <x:c r="A603" s="6" t="n"/>
@@ -32088,6 +34509,10 @@
       <x:c r="O603" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P603" t="str"/>
+      <x:c r="Q603" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="604">
       <x:c r="A604" s="6" t="n"/>
@@ -32139,6 +34564,10 @@
       <x:c r="O604" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P604" t="str"/>
+      <x:c r="Q604" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="605">
       <x:c r="A605" s="6" t="n"/>
@@ -32190,6 +34619,10 @@
       <x:c r="O605" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P605" t="str"/>
+      <x:c r="Q605" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="606">
       <x:c r="A606" s="6" t="n"/>
@@ -32241,6 +34674,10 @@
       <x:c r="O606" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P606" t="str"/>
+      <x:c r="Q606" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="607">
       <x:c r="A607" s="6" t="n"/>
@@ -32292,6 +34729,10 @@
       <x:c r="O607" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P607" t="str"/>
+      <x:c r="Q607" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="608">
       <x:c r="A608" s="6" t="n"/>
@@ -32343,6 +34784,10 @@
       <x:c r="O608" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P608" t="str"/>
+      <x:c r="Q608" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="609">
       <x:c r="A609" s="6" t="n"/>
@@ -32394,6 +34839,10 @@
       <x:c r="O609" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P609" t="str"/>
+      <x:c r="Q609" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="610">
       <x:c r="A610" s="6" t="n"/>
@@ -32445,6 +34894,10 @@
       <x:c r="O610" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P610" t="str"/>
+      <x:c r="Q610" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="611">
       <x:c r="A611" s="6" t="n"/>
@@ -32496,6 +34949,10 @@
       <x:c r="O611" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P611" t="str"/>
+      <x:c r="Q611" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="612">
       <x:c r="A612" s="6" t="n"/>
@@ -32547,6 +35004,10 @@
       <x:c r="O612" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P612" t="str"/>
+      <x:c r="Q612" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="613">
       <x:c r="A613" s="6" t="n"/>
@@ -32598,6 +35059,10 @@
       <x:c r="O613" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P613" t="str"/>
+      <x:c r="Q613" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="614">
       <x:c r="A614" s="6" t="n"/>
@@ -32649,6 +35114,10 @@
       <x:c r="O614" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P614" t="str"/>
+      <x:c r="Q614" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="615">
       <x:c r="A615" s="6" t="n"/>
@@ -32700,6 +35169,10 @@
       <x:c r="O615" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P615" t="str"/>
+      <x:c r="Q615" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="616">
       <x:c r="A616" s="6" t="n"/>
@@ -32751,6 +35224,10 @@
       <x:c r="O616" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P616" t="str"/>
+      <x:c r="Q616" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="617">
       <x:c r="A617" s="6" t="n"/>
@@ -32806,6 +35283,10 @@
       <x:c r="O617" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P617" t="str"/>
+      <x:c r="Q617" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="618">
       <x:c r="A618" s="6" t="n"/>
@@ -32861,6 +35342,10 @@
       <x:c r="O618" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P618" t="str"/>
+      <x:c r="Q618" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="619">
       <x:c r="A619" s="6" t="n"/>
@@ -32916,6 +35401,10 @@
       <x:c r="O619" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P619" t="str"/>
+      <x:c r="Q619" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="620">
       <x:c r="A620" s="6" t="n"/>
@@ -32967,6 +35456,10 @@
       <x:c r="O620" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P620" t="str"/>
+      <x:c r="Q620" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="621">
       <x:c r="A621" s="6" t="n"/>
@@ -33018,6 +35511,10 @@
       <x:c r="O621" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P621" t="str"/>
+      <x:c r="Q621" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="622">
       <x:c r="A622" s="6" t="n"/>
@@ -33069,6 +35566,10 @@
       <x:c r="O622" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P622" t="str"/>
+      <x:c r="Q622" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="623">
       <x:c r="A623" s="6" t="n"/>
@@ -33120,6 +35621,10 @@
       <x:c r="O623" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P623" t="str"/>
+      <x:c r="Q623" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="624">
       <x:c r="A624" s="6" t="n"/>
@@ -33171,6 +35676,10 @@
       <x:c r="O624" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P624" t="str"/>
+      <x:c r="Q624" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="625">
       <x:c r="A625" s="6" t="n"/>
@@ -33222,6 +35731,10 @@
       <x:c r="O625" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P625" t="str"/>
+      <x:c r="Q625" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="626">
       <x:c r="A626" s="6" t="n"/>
@@ -33273,6 +35786,10 @@
       <x:c r="O626" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P626" t="str"/>
+      <x:c r="Q626" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="627">
       <x:c r="A627" s="6" t="n"/>
@@ -33324,6 +35841,10 @@
       <x:c r="O627" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P627" t="str"/>
+      <x:c r="Q627" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="628">
       <x:c r="A628" s="6" t="n"/>
@@ -33375,6 +35896,10 @@
       <x:c r="O628" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P628" t="str"/>
+      <x:c r="Q628" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="629">
       <x:c r="A629" s="6" t="n"/>
@@ -33426,6 +35951,10 @@
       <x:c r="O629" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P629" t="str"/>
+      <x:c r="Q629" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="630">
       <x:c r="A630" s="6" t="n"/>
@@ -33477,6 +36006,10 @@
       <x:c r="O630" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P630" t="str"/>
+      <x:c r="Q630" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="631">
       <x:c r="A631" s="6" t="n"/>
@@ -33532,6 +36065,10 @@
       <x:c r="O631" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P631" t="str"/>
+      <x:c r="Q631" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="632">
       <x:c r="A632" s="6" t="n"/>
@@ -33587,6 +36124,10 @@
       <x:c r="O632" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P632" t="str"/>
+      <x:c r="Q632" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="633">
       <x:c r="A633" s="6" t="n"/>
@@ -33638,6 +36179,10 @@
       <x:c r="O633" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P633" t="str"/>
+      <x:c r="Q633" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="634">
       <x:c r="A634" s="6" t="n"/>
@@ -33689,6 +36234,10 @@
       <x:c r="O634" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P634" t="str"/>
+      <x:c r="Q634" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="635">
       <x:c r="A635" s="6" t="n"/>
@@ -33740,6 +36289,10 @@
       <x:c r="O635" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P635" t="str"/>
+      <x:c r="Q635" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="636">
       <x:c r="A636" s="6" t="n"/>
@@ -33791,6 +36344,10 @@
       <x:c r="O636" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P636" t="str"/>
+      <x:c r="Q636" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="637">
       <x:c r="A637" s="6" t="n"/>
@@ -33842,6 +36399,10 @@
       <x:c r="O637" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P637" t="str"/>
+      <x:c r="Q637" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="638">
       <x:c r="A638" s="6" t="n"/>
@@ -33893,6 +36454,10 @@
       <x:c r="O638" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P638" t="str"/>
+      <x:c r="Q638" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="639">
       <x:c r="A639" s="6" t="n"/>
@@ -33944,6 +36509,10 @@
       <x:c r="O639" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P639" t="str"/>
+      <x:c r="Q639" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="640">
       <x:c r="A640" s="6" t="n"/>
@@ -33995,6 +36564,10 @@
       <x:c r="O640" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P640" t="str"/>
+      <x:c r="Q640" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="641">
       <x:c r="A641" s="6" t="n"/>
@@ -34046,6 +36619,10 @@
       <x:c r="O641" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P641" t="str"/>
+      <x:c r="Q641" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="642">
       <x:c r="A642" s="6" t="n"/>
@@ -34097,6 +36674,10 @@
       <x:c r="O642" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P642" t="str"/>
+      <x:c r="Q642" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="643">
       <x:c r="A643" s="6" t="n"/>
@@ -34152,6 +36733,10 @@
       <x:c r="O643" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P643" t="str"/>
+      <x:c r="Q643" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="644">
       <x:c r="A644" s="6" t="n"/>
@@ -34207,6 +36792,10 @@
       <x:c r="O644" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P644" t="str"/>
+      <x:c r="Q644" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="645">
       <x:c r="A645" s="6" t="n"/>
@@ -34262,6 +36851,10 @@
       <x:c r="O645" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P645" t="str"/>
+      <x:c r="Q645" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="646">
       <x:c r="A646" s="6" t="n"/>
@@ -34317,6 +36910,10 @@
       <x:c r="O646" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P646" t="str"/>
+      <x:c r="Q646" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="647">
       <x:c r="A647" s="6" t="n"/>
@@ -34372,6 +36969,10 @@
       <x:c r="O647" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P647" t="str"/>
+      <x:c r="Q647" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="648">
       <x:c r="A648" s="6" t="n"/>
@@ -34427,6 +37028,10 @@
       <x:c r="O648" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P648" t="str"/>
+      <x:c r="Q648" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="649">
       <x:c r="A649" s="6" t="n"/>
@@ -34482,6 +37087,10 @@
       <x:c r="O649" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P649" t="str"/>
+      <x:c r="Q649" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="650">
       <x:c r="A650" s="6" t="n"/>
@@ -34537,6 +37146,10 @@
       <x:c r="O650" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P650" t="str"/>
+      <x:c r="Q650" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="651">
       <x:c r="A651" s="6" t="n"/>
@@ -34592,6 +37205,10 @@
       <x:c r="O651" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P651" t="str"/>
+      <x:c r="Q651" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="652">
       <x:c r="A652" s="6" t="n"/>
@@ -34647,6 +37264,10 @@
       <x:c r="O652" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P652" t="str"/>
+      <x:c r="Q652" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="653">
       <x:c r="A653" s="6" t="n"/>
@@ -34702,6 +37323,10 @@
       <x:c r="O653" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P653" t="str"/>
+      <x:c r="Q653" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="654">
       <x:c r="A654" s="6" t="n"/>
@@ -34757,6 +37382,10 @@
       <x:c r="O654" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P654" t="str"/>
+      <x:c r="Q654" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="655">
       <x:c r="A655" s="6" t="n"/>
@@ -34812,6 +37441,10 @@
       <x:c r="O655" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P655" t="str"/>
+      <x:c r="Q655" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="656">
       <x:c r="A656" s="6" t="n"/>
@@ -34867,6 +37500,10 @@
       <x:c r="O656" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P656" t="str"/>
+      <x:c r="Q656" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="657">
       <x:c r="A657" s="6" t="n"/>
@@ -34922,6 +37559,10 @@
       <x:c r="O657" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P657" t="str"/>
+      <x:c r="Q657" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="658">
       <x:c r="A658" s="6" t="n"/>
@@ -34977,6 +37618,10 @@
       <x:c r="O658" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P658" t="str"/>
+      <x:c r="Q658" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="659">
       <x:c r="A659" s="6" t="n"/>
@@ -35032,6 +37677,10 @@
       <x:c r="O659" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P659" t="str"/>
+      <x:c r="Q659" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="660">
       <x:c r="A660" s="6" t="n"/>
@@ -35087,6 +37736,10 @@
       <x:c r="O660" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P660" t="str"/>
+      <x:c r="Q660" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="661">
       <x:c r="A661" s="6" t="n"/>
@@ -35142,6 +37795,10 @@
       <x:c r="O661" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P661" t="str"/>
+      <x:c r="Q661" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="662">
       <x:c r="A662" s="6" t="n"/>
@@ -35197,6 +37854,10 @@
       <x:c r="O662" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P662" t="str"/>
+      <x:c r="Q662" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="663">
       <x:c r="A663" s="6" t="n"/>
@@ -35252,6 +37913,10 @@
       <x:c r="O663" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P663" t="str"/>
+      <x:c r="Q663" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="664">
       <x:c r="A664" s="6" t="n"/>
@@ -35307,6 +37972,10 @@
       <x:c r="O664" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P664" t="str"/>
+      <x:c r="Q664" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="665">
       <x:c r="A665" s="6" t="n"/>
@@ -35358,6 +38027,10 @@
       <x:c r="O665" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P665" t="str"/>
+      <x:c r="Q665" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="666">
       <x:c r="A666" s="6" t="n"/>
@@ -35409,6 +38082,10 @@
       <x:c r="O666" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P666" t="str"/>
+      <x:c r="Q666" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="667">
       <x:c r="A667" s="6" t="n"/>
@@ -35460,6 +38137,10 @@
       <x:c r="O667" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P667" t="str"/>
+      <x:c r="Q667" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="668">
       <x:c r="A668" s="6" t="n"/>
@@ -35511,6 +38192,10 @@
       <x:c r="O668" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P668" t="str"/>
+      <x:c r="Q668" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="669">
       <x:c r="A669" s="6" t="n"/>
@@ -35562,6 +38247,10 @@
       <x:c r="O669" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P669" t="str"/>
+      <x:c r="Q669" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="670">
       <x:c r="A670" s="6" t="n"/>
@@ -35613,6 +38302,10 @@
       <x:c r="O670" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P670" t="str"/>
+      <x:c r="Q670" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="671">
       <x:c r="A671" s="6" t="n"/>
@@ -35664,6 +38357,10 @@
       <x:c r="O671" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P671" t="str"/>
+      <x:c r="Q671" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="672">
       <x:c r="A672" s="6" t="n"/>
@@ -35715,6 +38412,10 @@
       <x:c r="O672" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P672" t="str"/>
+      <x:c r="Q672" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="673">
       <x:c r="A673" s="6" t="n"/>
@@ -35766,6 +38467,10 @@
       <x:c r="O673" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P673" t="str"/>
+      <x:c r="Q673" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="674">
       <x:c r="A674" s="6" t="n"/>
@@ -35817,6 +38522,10 @@
       <x:c r="O674" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P674" t="str"/>
+      <x:c r="Q674" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="675">
       <x:c r="A675" s="6" t="n"/>
@@ -35868,6 +38577,10 @@
       <x:c r="O675" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P675" t="str"/>
+      <x:c r="Q675" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="676">
       <x:c r="A676" s="6" t="n"/>
@@ -35919,6 +38632,10 @@
       <x:c r="O676" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P676" t="str"/>
+      <x:c r="Q676" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="677">
       <x:c r="A677" s="6" t="n"/>
@@ -35970,6 +38687,10 @@
       <x:c r="O677" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P677" t="str"/>
+      <x:c r="Q677" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="678">
       <x:c r="A678" s="6" t="n"/>
@@ -36021,6 +38742,10 @@
       <x:c r="O678" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P678" t="str"/>
+      <x:c r="Q678" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="679">
       <x:c r="A679" s="6" t="n"/>
@@ -36072,6 +38797,10 @@
       <x:c r="O679" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P679" t="str"/>
+      <x:c r="Q679" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="680">
       <x:c r="A680" s="6" t="n"/>
@@ -36123,6 +38852,10 @@
       <x:c r="O680" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P680" t="str"/>
+      <x:c r="Q680" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="681">
       <x:c r="A681" s="6" t="n"/>
@@ -36174,6 +38907,10 @@
       <x:c r="O681" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P681" t="str"/>
+      <x:c r="Q681" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="682">
       <x:c r="A682" s="6" t="n"/>
@@ -36225,6 +38962,10 @@
       <x:c r="O682" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P682" t="str"/>
+      <x:c r="Q682" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="683">
       <x:c r="A683" s="6" t="n"/>
@@ -36276,6 +39017,10 @@
       <x:c r="O683" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P683" t="str"/>
+      <x:c r="Q683" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="684">
       <x:c r="A684" s="6" t="n"/>
@@ -36327,6 +39072,10 @@
       <x:c r="O684" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P684" t="str"/>
+      <x:c r="Q684" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="685">
       <x:c r="A685" s="6" t="n"/>
@@ -36378,6 +39127,10 @@
       <x:c r="O685" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P685" t="str"/>
+      <x:c r="Q685" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="686">
       <x:c r="A686" s="6" t="n"/>
@@ -36429,6 +39182,10 @@
       <x:c r="O686" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P686" t="str"/>
+      <x:c r="Q686" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="687">
       <x:c r="A687" s="6" t="n"/>
@@ -36480,6 +39237,10 @@
       <x:c r="O687" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P687" t="str"/>
+      <x:c r="Q687" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="688">
       <x:c r="A688" s="6" t="n"/>
@@ -36531,6 +39292,10 @@
       <x:c r="O688" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P688" t="str"/>
+      <x:c r="Q688" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="689">
       <x:c r="A689" s="6" t="n"/>
@@ -36582,6 +39347,10 @@
       <x:c r="O689" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P689" t="str"/>
+      <x:c r="Q689" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="690">
       <x:c r="A690" s="6" t="n"/>
@@ -36633,6 +39402,10 @@
       <x:c r="O690" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P690" t="str"/>
+      <x:c r="Q690" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="691">
       <x:c r="A691" s="6" t="n"/>
@@ -36684,6 +39457,10 @@
       <x:c r="O691" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P691" t="str"/>
+      <x:c r="Q691" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="692">
       <x:c r="A692" s="6" t="n"/>
@@ -36735,6 +39512,10 @@
       <x:c r="O692" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P692" t="str"/>
+      <x:c r="Q692" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="693">
       <x:c r="A693" s="6" t="n"/>
@@ -36786,6 +39567,10 @@
       <x:c r="O693" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P693" t="str"/>
+      <x:c r="Q693" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="694">
       <x:c r="A694" s="6" t="n"/>
@@ -36837,6 +39622,10 @@
       <x:c r="O694" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P694" t="str"/>
+      <x:c r="Q694" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="695">
       <x:c r="A695" s="6" t="n"/>
@@ -36888,6 +39677,10 @@
       <x:c r="O695" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P695" t="str"/>
+      <x:c r="Q695" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="696">
       <x:c r="A696" s="6" t="n"/>
@@ -36943,6 +39736,10 @@
       <x:c r="O696" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P696" t="str"/>
+      <x:c r="Q696" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="697">
       <x:c r="A697" s="6" t="n"/>
@@ -36998,6 +39795,10 @@
       <x:c r="O697" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P697" t="str"/>
+      <x:c r="Q697" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="698">
       <x:c r="A698" s="6" t="n"/>
@@ -37053,6 +39854,10 @@
       <x:c r="O698" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P698" t="str"/>
+      <x:c r="Q698" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="699">
       <x:c r="A699" s="6" t="n"/>
@@ -37104,6 +39909,10 @@
       <x:c r="O699" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P699" t="str"/>
+      <x:c r="Q699" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="700">
       <x:c r="A700" s="6" t="n"/>
@@ -37155,6 +39964,10 @@
       <x:c r="O700" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P700" t="str"/>
+      <x:c r="Q700" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="701">
       <x:c r="A701" s="6" t="n"/>
@@ -37206,6 +40019,10 @@
       <x:c r="O701" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P701" t="str"/>
+      <x:c r="Q701" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="702">
       <x:c r="A702" s="6" t="n"/>
@@ -37257,6 +40074,10 @@
       <x:c r="O702" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P702" t="str"/>
+      <x:c r="Q702" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="703">
       <x:c r="A703" s="6" t="n"/>
@@ -37308,6 +40129,10 @@
       <x:c r="O703" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P703" t="str"/>
+      <x:c r="Q703" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="704">
       <x:c r="A704" s="6" t="n"/>
@@ -37359,6 +40184,10 @@
       <x:c r="O704" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P704" t="str"/>
+      <x:c r="Q704" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="705">
       <x:c r="A705" s="6" t="n"/>
@@ -37410,6 +40239,10 @@
       <x:c r="O705" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P705" t="str"/>
+      <x:c r="Q705" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="706">
       <x:c r="A706" s="6" t="n"/>
@@ -37461,6 +40294,10 @@
       <x:c r="O706" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P706" t="str"/>
+      <x:c r="Q706" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="707">
       <x:c r="A707" s="6" t="n"/>
@@ -37512,6 +40349,10 @@
       <x:c r="O707" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P707" t="str"/>
+      <x:c r="Q707" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="708">
       <x:c r="A708" s="6" t="n"/>
@@ -37563,6 +40404,10 @@
       <x:c r="O708" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P708" t="str"/>
+      <x:c r="Q708" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="709">
       <x:c r="A709" s="6" t="n"/>
@@ -37614,6 +40459,10 @@
       <x:c r="O709" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P709" t="str"/>
+      <x:c r="Q709" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="710">
       <x:c r="A710" s="6" t="n"/>
@@ -37669,6 +40518,10 @@
       <x:c r="O710" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P710" t="str"/>
+      <x:c r="Q710" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="711">
       <x:c r="A711" s="6" t="n"/>
@@ -37724,6 +40577,10 @@
       <x:c r="O711" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P711" t="str"/>
+      <x:c r="Q711" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="712">
       <x:c r="A712" s="6" t="n"/>
@@ -37775,6 +40632,10 @@
       <x:c r="O712" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P712" t="str"/>
+      <x:c r="Q712" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="713">
       <x:c r="A713" s="6" t="n"/>
@@ -37826,6 +40687,10 @@
       <x:c r="O713" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P713" t="str"/>
+      <x:c r="Q713" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="714">
       <x:c r="A714" s="6" t="n"/>
@@ -37877,6 +40742,10 @@
       <x:c r="O714" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P714" t="str"/>
+      <x:c r="Q714" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="715">
       <x:c r="A715" s="6" t="n"/>
@@ -37928,6 +40797,10 @@
       <x:c r="O715" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P715" t="str"/>
+      <x:c r="Q715" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="716">
       <x:c r="A716" s="6" t="n"/>
@@ -37979,6 +40852,10 @@
       <x:c r="O716" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P716" t="str"/>
+      <x:c r="Q716" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="717">
       <x:c r="A717" s="6" t="n"/>
@@ -38030,6 +40907,10 @@
       <x:c r="O717" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P717" t="str"/>
+      <x:c r="Q717" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="718">
       <x:c r="A718" s="6" t="n"/>
@@ -38081,6 +40962,10 @@
       <x:c r="O718" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P718" t="str"/>
+      <x:c r="Q718" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="719">
       <x:c r="A719" s="6" t="n"/>
@@ -38132,6 +41017,10 @@
       <x:c r="O719" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P719" t="str"/>
+      <x:c r="Q719" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="720">
       <x:c r="A720" s="6" t="n"/>
@@ -38183,6 +41072,10 @@
       <x:c r="O720" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P720" t="str"/>
+      <x:c r="Q720" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="721">
       <x:c r="A721" s="6" t="n"/>
@@ -38234,6 +41127,10 @@
       <x:c r="O721" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P721" t="str"/>
+      <x:c r="Q721" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="722">
       <x:c r="A722" s="6" t="n"/>
@@ -38289,6 +41186,10 @@
       <x:c r="O722" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P722" t="str"/>
+      <x:c r="Q722" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="723">
       <x:c r="A723" s="6" t="n"/>
@@ -38344,6 +41245,10 @@
       <x:c r="O723" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P723" t="str"/>
+      <x:c r="Q723" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="724">
       <x:c r="A724" s="6" t="n"/>
@@ -38399,6 +41304,10 @@
       <x:c r="O724" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P724" t="str"/>
+      <x:c r="Q724" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="725">
       <x:c r="A725" s="6" t="n"/>
@@ -38454,6 +41363,10 @@
       <x:c r="O725" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P725" t="str"/>
+      <x:c r="Q725" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="726">
       <x:c r="A726" s="6" t="n"/>
@@ -38509,6 +41422,10 @@
       <x:c r="O726" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P726" t="str"/>
+      <x:c r="Q726" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="727">
       <x:c r="A727" s="6" t="n"/>
@@ -38564,6 +41481,10 @@
       <x:c r="O727" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P727" t="str"/>
+      <x:c r="Q727" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="728">
       <x:c r="A728" s="6" t="n"/>
@@ -38619,6 +41540,10 @@
       <x:c r="O728" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P728" t="str"/>
+      <x:c r="Q728" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="729">
       <x:c r="A729" s="6" t="n"/>
@@ -38674,6 +41599,10 @@
       <x:c r="O729" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P729" t="str"/>
+      <x:c r="Q729" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="730">
       <x:c r="A730" s="6" t="n"/>
@@ -38729,6 +41658,10 @@
       <x:c r="O730" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P730" t="str"/>
+      <x:c r="Q730" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="731">
       <x:c r="A731" s="6" t="n"/>
@@ -38784,6 +41717,10 @@
       <x:c r="O731" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P731" t="str"/>
+      <x:c r="Q731" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="732">
       <x:c r="A732" s="6" t="n"/>
@@ -38839,6 +41776,10 @@
       <x:c r="O732" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P732" t="str"/>
+      <x:c r="Q732" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="733">
       <x:c r="A733" s="6" t="n"/>
@@ -38894,6 +41835,10 @@
       <x:c r="O733" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P733" t="str"/>
+      <x:c r="Q733" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="734">
       <x:c r="A734" s="6" t="n"/>
@@ -38949,6 +41894,10 @@
       <x:c r="O734" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P734" t="str"/>
+      <x:c r="Q734" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="735">
       <x:c r="A735" s="6" t="n"/>
@@ -39004,6 +41953,10 @@
       <x:c r="O735" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P735" t="str"/>
+      <x:c r="Q735" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="736">
       <x:c r="A736" s="6" t="n"/>
@@ -39059,6 +42012,10 @@
       <x:c r="O736" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P736" t="str"/>
+      <x:c r="Q736" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="737">
       <x:c r="A737" s="6" t="n"/>
@@ -39114,6 +42071,10 @@
       <x:c r="O737" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P737" t="str"/>
+      <x:c r="Q737" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="738">
       <x:c r="A738" s="6" t="n"/>
@@ -39169,6 +42130,10 @@
       <x:c r="O738" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P738" t="str"/>
+      <x:c r="Q738" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="739">
       <x:c r="A739" s="6" t="n"/>
@@ -39224,6 +42189,10 @@
       <x:c r="O739" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P739" t="str"/>
+      <x:c r="Q739" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="740">
       <x:c r="A740" s="6" t="n"/>
@@ -39279,6 +42248,10 @@
       <x:c r="O740" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P740" t="str"/>
+      <x:c r="Q740" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="741">
       <x:c r="A741" s="6" t="n"/>
@@ -39334,6 +42307,10 @@
       <x:c r="O741" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P741" t="str"/>
+      <x:c r="Q741" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="742">
       <x:c r="A742" s="6" t="n"/>
@@ -39389,6 +42366,10 @@
       <x:c r="O742" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P742" t="str"/>
+      <x:c r="Q742" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="743">
       <x:c r="A743" s="6" t="n"/>
@@ -39444,6 +42425,10 @@
       <x:c r="O743" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P743" t="str"/>
+      <x:c r="Q743" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="744">
       <x:c r="A744" s="6" t="n"/>
@@ -39495,6 +42480,10 @@
       <x:c r="O744" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P744" t="str"/>
+      <x:c r="Q744" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="745">
       <x:c r="A745" s="6" t="n"/>
@@ -39546,6 +42535,10 @@
       <x:c r="O745" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P745" t="str"/>
+      <x:c r="Q745" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="746">
       <x:c r="A746" s="6" t="n"/>
@@ -39597,6 +42590,10 @@
       <x:c r="O746" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P746" t="str"/>
+      <x:c r="Q746" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="747">
       <x:c r="A747" s="6" t="n"/>
@@ -39648,6 +42645,10 @@
       <x:c r="O747" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P747" t="str"/>
+      <x:c r="Q747" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="748">
       <x:c r="A748" s="6" t="n"/>
@@ -39699,6 +42700,10 @@
       <x:c r="O748" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P748" t="str"/>
+      <x:c r="Q748" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="749">
       <x:c r="A749" s="6" t="n"/>
@@ -39750,6 +42755,10 @@
       <x:c r="O749" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P749" t="str"/>
+      <x:c r="Q749" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="750">
       <x:c r="A750" s="6" t="n"/>
@@ -39801,6 +42810,10 @@
       <x:c r="O750" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P750" t="str"/>
+      <x:c r="Q750" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="751">
       <x:c r="A751" s="6" t="n"/>
@@ -39852,6 +42865,10 @@
       <x:c r="O751" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P751" t="str"/>
+      <x:c r="Q751" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="752">
       <x:c r="A752" s="6" t="n"/>
@@ -39903,6 +42920,10 @@
       <x:c r="O752" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P752" t="str"/>
+      <x:c r="Q752" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="753">
       <x:c r="A753" s="6" t="n"/>
@@ -39954,6 +42975,10 @@
       <x:c r="O753" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P753" t="str"/>
+      <x:c r="Q753" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="754">
       <x:c r="A754" s="6" t="n"/>
@@ -40005,6 +43030,10 @@
       <x:c r="O754" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P754" t="str"/>
+      <x:c r="Q754" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="755">
       <x:c r="A755" s="6" t="n"/>
@@ -40056,6 +43085,10 @@
       <x:c r="O755" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P755" t="str"/>
+      <x:c r="Q755" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="756">
       <x:c r="A756" s="6" t="n"/>
@@ -40107,6 +43140,10 @@
       <x:c r="O756" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P756" t="str"/>
+      <x:c r="Q756" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="757">
       <x:c r="A757" s="6" t="n"/>
@@ -40158,6 +43195,10 @@
       <x:c r="O757" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P757" t="str"/>
+      <x:c r="Q757" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="758">
       <x:c r="A758" s="6" t="n"/>
@@ -40209,6 +43250,10 @@
       <x:c r="O758" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P758" t="str"/>
+      <x:c r="Q758" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="759">
       <x:c r="A759" s="6" t="n"/>
@@ -40260,6 +43305,10 @@
       <x:c r="O759" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P759" t="str"/>
+      <x:c r="Q759" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="760">
       <x:c r="A760" s="6" t="n"/>
@@ -40311,6 +43360,10 @@
       <x:c r="O760" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P760" t="str"/>
+      <x:c r="Q760" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="761">
       <x:c r="A761" s="6" t="n"/>
@@ -40362,6 +43415,10 @@
       <x:c r="O761" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P761" t="str"/>
+      <x:c r="Q761" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="762">
       <x:c r="A762" s="6" t="n"/>
@@ -40413,6 +43470,10 @@
       <x:c r="O762" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P762" t="str"/>
+      <x:c r="Q762" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="763">
       <x:c r="A763" s="6" t="n"/>
@@ -40464,6 +43525,10 @@
       <x:c r="O763" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P763" t="str"/>
+      <x:c r="Q763" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="764">
       <x:c r="A764" s="6" t="n"/>
@@ -40515,6 +43580,10 @@
       <x:c r="O764" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P764" t="str"/>
+      <x:c r="Q764" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="765">
       <x:c r="A765" s="6" t="n"/>
@@ -40566,6 +43635,10 @@
       <x:c r="O765" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P765" t="str"/>
+      <x:c r="Q765" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="766">
       <x:c r="A766" s="6" t="n"/>
@@ -40617,6 +43690,10 @@
       <x:c r="O766" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P766" t="str"/>
+      <x:c r="Q766" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="767">
       <x:c r="A767" s="6" t="n"/>
@@ -40668,6 +43745,10 @@
       <x:c r="O767" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P767" t="str"/>
+      <x:c r="Q767" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="768">
       <x:c r="A768" s="6" t="n"/>
@@ -40719,6 +43800,10 @@
       <x:c r="O768" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P768" t="str"/>
+      <x:c r="Q768" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="769">
       <x:c r="A769" s="6" t="n"/>
@@ -40770,6 +43855,10 @@
       <x:c r="O769" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P769" t="str"/>
+      <x:c r="Q769" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="770">
       <x:c r="A770" s="6" t="n"/>
@@ -40821,6 +43910,10 @@
       <x:c r="O770" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P770" t="str"/>
+      <x:c r="Q770" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="771">
       <x:c r="A771" s="6" t="n"/>
@@ -40872,6 +43965,10 @@
       <x:c r="O771" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P771" t="str"/>
+      <x:c r="Q771" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="772">
       <x:c r="A772" s="6" t="n"/>
@@ -40923,6 +44020,10 @@
       <x:c r="O772" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P772" t="str"/>
+      <x:c r="Q772" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="773">
       <x:c r="A773" s="6" t="n"/>
@@ -40974,6 +44075,10 @@
       <x:c r="O773" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P773" t="str"/>
+      <x:c r="Q773" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="774">
       <x:c r="A774" s="6" t="n"/>
@@ -41025,6 +44130,10 @@
       <x:c r="O774" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P774" t="str"/>
+      <x:c r="Q774" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="775">
       <x:c r="A775" s="6" t="n"/>
@@ -41080,6 +44189,10 @@
       <x:c r="O775" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P775" t="str"/>
+      <x:c r="Q775" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="776">
       <x:c r="A776" s="6" t="n"/>
@@ -41135,6 +44248,10 @@
       <x:c r="O776" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P776" t="str"/>
+      <x:c r="Q776" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="777">
       <x:c r="A777" s="6" t="n"/>
@@ -41190,6 +44307,10 @@
       <x:c r="O777" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P777" t="str"/>
+      <x:c r="Q777" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="778">
       <x:c r="A778" s="6" t="n"/>
@@ -41241,6 +44362,10 @@
       <x:c r="O778" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P778" t="str"/>
+      <x:c r="Q778" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="779">
       <x:c r="A779" s="6" t="n"/>
@@ -41292,6 +44417,10 @@
       <x:c r="O779" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P779" t="str"/>
+      <x:c r="Q779" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="780">
       <x:c r="A780" s="6" t="n"/>
@@ -41343,6 +44472,10 @@
       <x:c r="O780" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P780" t="str"/>
+      <x:c r="Q780" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="781">
       <x:c r="A781" s="6" t="n"/>
@@ -41394,6 +44527,10 @@
       <x:c r="O781" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P781" t="str"/>
+      <x:c r="Q781" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="782">
       <x:c r="A782" s="6" t="n"/>
@@ -41445,6 +44582,10 @@
       <x:c r="O782" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P782" t="str"/>
+      <x:c r="Q782" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="783">
       <x:c r="A783" s="6" t="n"/>
@@ -41496,6 +44637,10 @@
       <x:c r="O783" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P783" t="str"/>
+      <x:c r="Q783" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="784">
       <x:c r="A784" s="6" t="n"/>
@@ -41547,6 +44692,10 @@
       <x:c r="O784" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P784" t="str"/>
+      <x:c r="Q784" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="785">
       <x:c r="A785" s="6" t="n"/>
@@ -41598,6 +44747,10 @@
       <x:c r="O785" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P785" t="str"/>
+      <x:c r="Q785" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="786">
       <x:c r="A786" s="6" t="n"/>
@@ -41649,6 +44802,10 @@
       <x:c r="O786" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P786" t="str"/>
+      <x:c r="Q786" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="787">
       <x:c r="A787" s="6" t="n"/>
@@ -41700,6 +44857,10 @@
       <x:c r="O787" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P787" t="str"/>
+      <x:c r="Q787" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="788">
       <x:c r="A788" s="6" t="n"/>
@@ -41751,6 +44912,10 @@
       <x:c r="O788" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P788" t="str"/>
+      <x:c r="Q788" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="789">
       <x:c r="A789" s="6" t="n"/>
@@ -41806,6 +44971,10 @@
       <x:c r="O789" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P789" t="str"/>
+      <x:c r="Q789" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="790">
       <x:c r="A790" s="6" t="n"/>
@@ -41861,6 +45030,10 @@
       <x:c r="O790" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P790" t="str"/>
+      <x:c r="Q790" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="791">
       <x:c r="A791" s="6" t="n"/>
@@ -41912,6 +45085,10 @@
       <x:c r="O791" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P791" t="str"/>
+      <x:c r="Q791" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="792">
       <x:c r="A792" s="6" t="n"/>
@@ -41963,6 +45140,10 @@
       <x:c r="O792" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P792" t="str"/>
+      <x:c r="Q792" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="793">
       <x:c r="A793" s="6" t="n"/>
@@ -42014,6 +45195,10 @@
       <x:c r="O793" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P793" t="str"/>
+      <x:c r="Q793" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="794">
       <x:c r="A794" s="6" t="n"/>
@@ -42065,6 +45250,10 @@
       <x:c r="O794" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P794" t="str"/>
+      <x:c r="Q794" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="795">
       <x:c r="A795" s="6" t="n"/>
@@ -42116,6 +45305,10 @@
       <x:c r="O795" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P795" t="str"/>
+      <x:c r="Q795" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="796">
       <x:c r="A796" s="6" t="n"/>
@@ -42167,6 +45360,10 @@
       <x:c r="O796" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P796" t="str"/>
+      <x:c r="Q796" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="797">
       <x:c r="A797" s="6" t="n"/>
@@ -42218,6 +45415,10 @@
       <x:c r="O797" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P797" t="str"/>
+      <x:c r="Q797" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="798">
       <x:c r="A798" s="6" t="n"/>
@@ -42269,6 +45470,10 @@
       <x:c r="O798" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P798" t="str"/>
+      <x:c r="Q798" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="799">
       <x:c r="A799" s="6" t="n"/>
@@ -42320,6 +45525,10 @@
       <x:c r="O799" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P799" t="str"/>
+      <x:c r="Q799" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="800">
       <x:c r="A800" s="6" t="n"/>
@@ -42371,6 +45580,10 @@
       <x:c r="O800" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P800" t="str"/>
+      <x:c r="Q800" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="801">
       <x:c r="A801" s="6" t="n"/>
@@ -42426,6 +45639,10 @@
       <x:c r="O801" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P801" t="str"/>
+      <x:c r="Q801" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="802">
       <x:c r="A802" s="6" t="n"/>
@@ -42481,6 +45698,10 @@
       <x:c r="O802" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P802" t="str"/>
+      <x:c r="Q802" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="803">
       <x:c r="A803" s="6" t="n"/>
@@ -42536,6 +45757,10 @@
       <x:c r="O803" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P803" t="str"/>
+      <x:c r="Q803" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="804">
       <x:c r="A804" s="6" t="n"/>
@@ -42591,6 +45816,10 @@
       <x:c r="O804" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P804" t="str"/>
+      <x:c r="Q804" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="805">
       <x:c r="A805" s="6" t="n"/>
@@ -42646,6 +45875,10 @@
       <x:c r="O805" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="P805" t="str"/>
+      <x:c r="Q805" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="806">
       <x:c r="A806" s="6" t="n"/>
@@ -42701,6 +45934,10 @@
       <x:c r="O806" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P806" t="str"/>
+      <x:c r="Q806" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="807">
       <x:c r="A807" s="6" t="n"/>
@@ -42756,6 +45993,10 @@
       <x:c r="O807" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P807" t="str"/>
+      <x:c r="Q807" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="808">
       <x:c r="A808" s="6" t="n"/>
@@ -42811,6 +46052,10 @@
       <x:c r="O808" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
+      <x:c r="P808" t="str"/>
+      <x:c r="Q808" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="809">
       <x:c r="A809" s="6" t="n"/>
@@ -42866,6 +46111,10 @@
       <x:c r="O809" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P809" t="str"/>
+      <x:c r="Q809" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="810">
       <x:c r="A810" s="6" t="n"/>
@@ -42921,6 +46170,10 @@
       <x:c r="O810" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P810" t="str"/>
+      <x:c r="Q810" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="811">
       <x:c r="A811" s="6" t="n"/>
@@ -42976,6 +46229,10 @@
       <x:c r="O811" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
+      <x:c r="P811" t="str"/>
+      <x:c r="Q811" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="812">
       <x:c r="A812" s="6" t="n"/>
@@ -43031,6 +46288,10 @@
       <x:c r="O812" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P812" t="str"/>
+      <x:c r="Q812" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="813">
       <x:c r="A813" s="6" t="n"/>
@@ -43086,6 +46347,10 @@
       <x:c r="O813" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P813" t="str"/>
+      <x:c r="Q813" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="814">
       <x:c r="A814" s="6" t="n"/>
@@ -43141,6 +46406,10 @@
       <x:c r="O814" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P814" t="str"/>
+      <x:c r="Q814" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="815">
       <x:c r="A815" s="6" t="n"/>
@@ -43196,6 +46465,10 @@
       <x:c r="O815" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P815" t="str"/>
+      <x:c r="Q815" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="816">
       <x:c r="A816" s="6" t="n"/>
@@ -43251,6 +46524,10 @@
       <x:c r="O816" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P816" t="str"/>
+      <x:c r="Q816" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="817">
       <x:c r="A817" s="6" t="n"/>
@@ -43306,6 +46583,10 @@
       <x:c r="O817" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
+      <x:c r="P817" t="str"/>
+      <x:c r="Q817" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="818">
       <x:c r="A818" s="6" t="n"/>
@@ -43361,6 +46642,10 @@
       <x:c r="O818" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P818" t="str"/>
+      <x:c r="Q818" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="819">
       <x:c r="A819" s="6" t="n"/>
@@ -43416,6 +46701,10 @@
       <x:c r="O819" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P819" t="str"/>
+      <x:c r="Q819" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="820">
       <x:c r="A820" s="6" t="n"/>
@@ -43471,6 +46760,10 @@
       <x:c r="O820" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P820" t="str"/>
+      <x:c r="Q820" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="821">
       <x:c r="A821" s="6" t="n"/>
@@ -43526,6 +46819,10 @@
       <x:c r="O821" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P821" t="str"/>
+      <x:c r="Q821" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="822">
       <x:c r="A822" s="6" t="n"/>
@@ -43581,6 +46878,10 @@
       <x:c r="O822" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P822" t="str"/>
+      <x:c r="Q822" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="823">
       <x:c r="A823" s="6" t="n"/>
@@ -43632,6 +46933,10 @@
       <x:c r="O823" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P823" t="str"/>
+      <x:c r="Q823" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="824">
       <x:c r="A824" s="6" t="n"/>
@@ -43683,6 +46988,10 @@
       <x:c r="O824" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P824" t="str"/>
+      <x:c r="Q824" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="825">
       <x:c r="A825" s="6" t="n"/>
@@ -43734,6 +47043,10 @@
       <x:c r="O825" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P825" t="str"/>
+      <x:c r="Q825" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="826">
       <x:c r="A826" s="6" t="n"/>
@@ -43785,6 +47098,10 @@
       <x:c r="O826" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P826" t="str"/>
+      <x:c r="Q826" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="827">
       <x:c r="A827" s="6" t="n"/>
@@ -43836,6 +47153,10 @@
       <x:c r="O827" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P827" t="str"/>
+      <x:c r="Q827" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="828">
       <x:c r="A828" s="6" t="n"/>
@@ -43887,6 +47208,10 @@
       <x:c r="O828" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P828" t="str"/>
+      <x:c r="Q828" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="829">
       <x:c r="A829" s="6" t="n"/>
@@ -43938,6 +47263,10 @@
       <x:c r="O829" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P829" t="str"/>
+      <x:c r="Q829" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="830">
       <x:c r="A830" s="6" t="n"/>
@@ -43989,6 +47318,10 @@
       <x:c r="O830" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P830" t="str"/>
+      <x:c r="Q830" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="831">
       <x:c r="A831" s="6" t="n"/>
@@ -44040,6 +47373,10 @@
       <x:c r="O831" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P831" t="str"/>
+      <x:c r="Q831" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="832">
       <x:c r="A832" s="6" t="n"/>
@@ -44091,6 +47428,10 @@
       <x:c r="O832" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P832" t="str"/>
+      <x:c r="Q832" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="833">
       <x:c r="A833" s="6" t="n"/>
@@ -44142,6 +47483,10 @@
       <x:c r="O833" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P833" t="str"/>
+      <x:c r="Q833" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="834">
       <x:c r="A834" s="6" t="n"/>
@@ -44193,6 +47538,10 @@
       <x:c r="O834" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P834" t="str"/>
+      <x:c r="Q834" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="835">
       <x:c r="A835" s="6" t="n"/>
@@ -44244,6 +47593,10 @@
       <x:c r="O835" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P835" t="str"/>
+      <x:c r="Q835" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="836">
       <x:c r="A836" s="6" t="n"/>
@@ -44295,6 +47648,10 @@
       <x:c r="O836" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P836" t="str"/>
+      <x:c r="Q836" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="837">
       <x:c r="A837" s="6" t="n"/>
@@ -44346,6 +47703,10 @@
       <x:c r="O837" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P837" t="str"/>
+      <x:c r="Q837" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="838">
       <x:c r="A838" s="6" t="n"/>
@@ -44397,6 +47758,10 @@
       <x:c r="O838" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P838" t="str"/>
+      <x:c r="Q838" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="839">
       <x:c r="A839" s="6" t="n"/>
@@ -44448,6 +47813,10 @@
       <x:c r="O839" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P839" t="str"/>
+      <x:c r="Q839" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="840">
       <x:c r="A840" s="6" t="n"/>
@@ -44499,6 +47868,10 @@
       <x:c r="O840" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P840" t="str"/>
+      <x:c r="Q840" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="841">
       <x:c r="A841" s="6" t="n"/>
@@ -44550,6 +47923,10 @@
       <x:c r="O841" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P841" t="str"/>
+      <x:c r="Q841" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="842">
       <x:c r="A842" s="6" t="n"/>
@@ -44601,6 +47978,10 @@
       <x:c r="O842" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P842" t="str"/>
+      <x:c r="Q842" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="843">
       <x:c r="A843" s="6" t="n"/>
@@ -44652,6 +48033,10 @@
       <x:c r="O843" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P843" t="str"/>
+      <x:c r="Q843" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="844">
       <x:c r="A844" s="6" t="n"/>
@@ -44703,6 +48088,10 @@
       <x:c r="O844" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P844" t="str"/>
+      <x:c r="Q844" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="845">
       <x:c r="A845" s="6" t="n"/>
@@ -44754,6 +48143,10 @@
       <x:c r="O845" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P845" t="str"/>
+      <x:c r="Q845" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="846">
       <x:c r="A846" s="6" t="n"/>
@@ -44805,6 +48198,10 @@
       <x:c r="O846" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P846" t="str"/>
+      <x:c r="Q846" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="847">
       <x:c r="A847" s="6" t="n"/>
@@ -44856,6 +48253,10 @@
       <x:c r="O847" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P847" t="str"/>
+      <x:c r="Q847" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="848">
       <x:c r="A848" s="6" t="n"/>
@@ -44907,6 +48308,10 @@
       <x:c r="O848" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P848" t="str"/>
+      <x:c r="Q848" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="849">
       <x:c r="A849" s="6" t="n"/>
@@ -44958,6 +48363,10 @@
       <x:c r="O849" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P849" t="str"/>
+      <x:c r="Q849" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="850">
       <x:c r="A850" s="6" t="n"/>
@@ -45009,6 +48418,10 @@
       <x:c r="O850" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P850" t="str"/>
+      <x:c r="Q850" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="851">
       <x:c r="A851" s="6" t="n"/>
@@ -45060,6 +48473,10 @@
       <x:c r="O851" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P851" t="str"/>
+      <x:c r="Q851" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="852">
       <x:c r="A852" s="6" t="n"/>
@@ -45111,6 +48528,10 @@
       <x:c r="O852" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P852" t="str"/>
+      <x:c r="Q852" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="853">
       <x:c r="A853" s="6" t="n"/>
@@ -45162,6 +48583,10 @@
       <x:c r="O853" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P853" t="str"/>
+      <x:c r="Q853" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="854">
       <x:c r="A854" s="6" t="n"/>
@@ -45217,6 +48642,10 @@
       <x:c r="O854" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P854" t="str"/>
+      <x:c r="Q854" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="855">
       <x:c r="A855" s="6" t="n"/>
@@ -45272,6 +48701,10 @@
       <x:c r="O855" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P855" t="str"/>
+      <x:c r="Q855" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="856">
       <x:c r="A856" s="6" t="n"/>
@@ -45327,6 +48760,10 @@
       <x:c r="O856" s="6" t="n">
         <x:v>5.2</x:v>
       </x:c>
+      <x:c r="P856" t="str"/>
+      <x:c r="Q856" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="857">
       <x:c r="A857" s="6" t="n"/>
@@ -45378,6 +48815,10 @@
       <x:c r="O857" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P857" t="str"/>
+      <x:c r="Q857" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="858">
       <x:c r="A858" s="6" t="n"/>
@@ -45429,6 +48870,10 @@
       <x:c r="O858" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P858" t="str"/>
+      <x:c r="Q858" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="859">
       <x:c r="A859" s="6" t="n"/>
@@ -45480,6 +48925,10 @@
       <x:c r="O859" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P859" t="str"/>
+      <x:c r="Q859" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="860">
       <x:c r="A860" s="6" t="n"/>
@@ -45531,6 +48980,10 @@
       <x:c r="O860" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P860" t="str"/>
+      <x:c r="Q860" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="861">
       <x:c r="A861" s="6" t="n"/>
@@ -45582,6 +49035,10 @@
       <x:c r="O861" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P861" t="str"/>
+      <x:c r="Q861" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="862">
       <x:c r="A862" s="6" t="n"/>
@@ -45633,6 +49090,10 @@
       <x:c r="O862" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P862" t="str"/>
+      <x:c r="Q862" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="863">
       <x:c r="A863" s="6" t="n"/>
@@ -45684,6 +49145,10 @@
       <x:c r="O863" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P863" t="str"/>
+      <x:c r="Q863" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="864">
       <x:c r="A864" s="6" t="n"/>
@@ -45735,6 +49200,10 @@
       <x:c r="O864" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P864" t="str"/>
+      <x:c r="Q864" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="865">
       <x:c r="A865" s="6" t="n"/>
@@ -45786,6 +49255,10 @@
       <x:c r="O865" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P865" t="str"/>
+      <x:c r="Q865" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="866">
       <x:c r="A866" s="6" t="n"/>
@@ -45837,6 +49310,10 @@
       <x:c r="O866" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P866" t="str"/>
+      <x:c r="Q866" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="867">
       <x:c r="A867" s="6" t="n"/>
@@ -45888,6 +49365,10 @@
       <x:c r="O867" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P867" t="str"/>
+      <x:c r="Q867" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="868">
       <x:c r="A868" s="6" t="n"/>
@@ -45943,6 +49424,10 @@
       <x:c r="O868" s="6" t="n">
         <x:v>0.55</x:v>
       </x:c>
+      <x:c r="P868" t="str"/>
+      <x:c r="Q868" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="869">
       <x:c r="A869" s="6" t="n"/>
@@ -45998,6 +49483,10 @@
       <x:c r="O869" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P869" t="str"/>
+      <x:c r="Q869" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="870">
       <x:c r="A870" s="6" t="n"/>
@@ -46049,6 +49538,10 @@
       <x:c r="O870" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P870" t="str"/>
+      <x:c r="Q870" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="871">
       <x:c r="A871" s="6" t="n"/>
@@ -46100,6 +49593,10 @@
       <x:c r="O871" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P871" t="str"/>
+      <x:c r="Q871" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="872">
       <x:c r="A872" s="6" t="n"/>
@@ -46151,6 +49648,10 @@
       <x:c r="O872" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P872" t="str"/>
+      <x:c r="Q872" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="873">
       <x:c r="A873" s="6" t="n"/>
@@ -46202,6 +49703,10 @@
       <x:c r="O873" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P873" t="str"/>
+      <x:c r="Q873" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="874">
       <x:c r="A874" s="6" t="n"/>
@@ -46253,6 +49758,10 @@
       <x:c r="O874" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P874" t="str"/>
+      <x:c r="Q874" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="875">
       <x:c r="A875" s="6" t="n"/>
@@ -46304,6 +49813,10 @@
       <x:c r="O875" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P875" t="str"/>
+      <x:c r="Q875" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="876">
       <x:c r="A876" s="6" t="n"/>
@@ -46355,6 +49868,10 @@
       <x:c r="O876" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P876" t="str"/>
+      <x:c r="Q876" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="877">
       <x:c r="A877" s="6" t="n"/>
@@ -46406,6 +49923,10 @@
       <x:c r="O877" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P877" t="str"/>
+      <x:c r="Q877" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="878">
       <x:c r="A878" s="6" t="n"/>
@@ -46457,6 +49978,10 @@
       <x:c r="O878" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P878" t="str"/>
+      <x:c r="Q878" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="879">
       <x:c r="A879" s="6" t="n"/>
@@ -46508,6 +50033,10 @@
       <x:c r="O879" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P879" t="str"/>
+      <x:c r="Q879" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="880">
       <x:c r="A880" s="6" t="n"/>
@@ -46563,6 +50092,10 @@
       <x:c r="O880" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P880" t="str"/>
+      <x:c r="Q880" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="881">
       <x:c r="A881" s="6" t="n"/>
@@ -46618,6 +50151,10 @@
       <x:c r="O881" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P881" t="str"/>
+      <x:c r="Q881" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="882">
       <x:c r="A882"/>
@@ -46661,6 +50198,108 @@
       <x:c r="O882" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P882" t="str"/>
+      <x:c r="Q882" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883">
+      <x:c r="A883"/>
+      <x:c r="B883" t="n">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="C883" t="str">
+        <x:v>wave_spawn_wave_level_02_single_shot_fighters_038_01</x:v>
+      </x:c>
+      <x:c r="D883" t="str">
+        <x:v>wave_level_02_single_shot_fighters_038</x:v>
+      </x:c>
+      <x:c r="E883" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F883" t="str">
+        <x:v>enemy_resource4</x:v>
+      </x:c>
+      <x:c r="G883" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H883" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I883" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J883" t="n">
+        <x:v>7.2</x:v>
+      </x:c>
+      <x:c r="K883" t="str">
+        <x:v>enemy_single_down@1.1+2.1</x:v>
+      </x:c>
+      <x:c r="L883" t="str">
+        <x:v>DriftLeft:rotateToPath=true,rotationOffset=90</x:v>
+      </x:c>
+      <x:c r="M883" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N883" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="O883" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P883"/>
+      <x:c r="Q883" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884">
+      <x:c r="A884"/>
+      <x:c r="B884" t="n">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="C884" t="str">
+        <x:v>wave_spawn_wave_level_02_single_shot_fighters_042_01</x:v>
+      </x:c>
+      <x:c r="D884" t="str">
+        <x:v>wave_level_02_single_shot_fighters_042</x:v>
+      </x:c>
+      <x:c r="E884" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F884" t="str">
+        <x:v>enemy_resource4</x:v>
+      </x:c>
+      <x:c r="G884" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H884" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I884" t="n">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="J884" t="n">
+        <x:v>7.2</x:v>
+      </x:c>
+      <x:c r="K884" t="str">
+        <x:v>enemy_single_down@1.1+2.1</x:v>
+      </x:c>
+      <x:c r="L884" t="str">
+        <x:v>DriftRight:rotateToPath=true,rotationOffset=90</x:v>
+      </x:c>
+      <x:c r="M884" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N884" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="O884" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P884"/>
+      <x:c r="Q884" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
